--- a/policies/4p-index/nepal-4p-index-master.xlsx
+++ b/policies/4p-index/nepal-4p-index-master.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Waste Mgmt Natl Policy 2079" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Solid Waste Mgmt Act 2068" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Sixteenth Plan 2024-29" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="EMF School Sector Program" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W30"/>
+  <dimension ref="A1:W34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3872,6 +3873,474 @@
       <c r="W30" s="2" t="inlineStr">
         <is>
           <t>Coded in force (S=1), unlike the qualitative program-level plastic/waste commitments above, because this is a specific, numerically quantified target with a fixed baseline and end-of-plan deadline that constitutes the government's own binding resource-allocation commitment -- not merely an aspirational directive to third parties. Scored as Planned government investment (0.80) per the P-scale's own example ('construction of a new waste management facility').</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="120" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Environmental Management Framework (EMF) for the School Sector Reform Plan (SSRP) / School Sector Program (SSP)</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adb.org/sites/default/files/project-documents/35174-082-nep-earfab.pdf</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>To integrate environmental assessment and environmental management planning into the planning, design, implementation and monitoring of school-infrastructure sub-projects under Nepal's School Sector Reform Program/School Sector Program (construction and rehabilitation of classrooms, District Education Office buildings, libraries/laboratories, toilets, water supply and seismic retrofitting), so as to identify and mitigate the adverse environmental impacts of that infrastructure work. In relation to plastics specifically, the Framework's environmental-impact mitigation table requires that solid waste (including plastic waste) generated in schools be properly segregated, minimised, reused/recycled and disposed of, and explicitly requires banning the use of plastic products in schools as a mitigation measure for hazardous-waste-related impacts.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>"Ban use of plastic products in schools." (Table: Anticipated Environmental Impacts / Mitigation Measures, row "Hazardous waste", under Section D "Anticipated Environmental Impacts"). This is a plastics-specific commitment but is not expressed as a quantified/numeric target (e.g. a percentage reduction), so Column E is coded 0.5 rather than 1.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>This is a donor-harmonised "Environmental Management Framework" (EMF) -- explicitly stated to be "equivalent to [ADB's] Environmental Assessment and Review Framework (EARF)" under ADB's 2009 Safeguard Policy Statement (footnote 2) -- prepared originally in May 2009 and updated (per this source document, ADB project document 35174-082-NEP) for the subsequent School Sector Program, with formal approval by the Ministry of Education (Table 6, item 1.1: "Approval of EMF for SSP -- MOE"). It is a programmatic safeguard framework tied to development-partner financing conditionality, not an Act of Parliament nor a Gazette-published executive regulation, so it does not qualify for the 0.75/1.0 tiers. It is coded at the higher "plan/programme incorporating quantifiable targets" tier (0.50) rather than the purely aspirational tier (0.25) because it contains multiple quantified operational elements -- an itemised implementation budget (Table 8) and monitoring indicators with defined frequencies (Tables 9-11) -- even though its specific plastics-related commitment (the in-school plastic ban) is not itself a quantified target.</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>education, waste management, health, water, construction, disaster risk management, energy</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>consumption, recycling, disposal, environmental leakage</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Section F.4, "Budgetary Requirement" / Table 8 "Cost for Implementation of EMF": a specific, itemised budget is set out for EMF implementation -- USD 5,000 for EMF translation, printing, publication and distribution; USD 25,000 for setting up a safeguard desk in DOE and DEOs; USD 100,000 for capacity building of MOE/DOE/DEOs/SMCs; environmental screening and EMP preparation costs of approximately USD 2,000 per Initial Environmental Examination (IEE) and USD 500 per Environmental Due Diligence Report (DDR), to be included in subproject costs; and environmental monitoring costs of USD 1,000 per subproject, also included in subproject costs. Coded 1 (ring-fenced) because this is a dedicated, itemised budget line created specifically for implementing this Framework's own environmental (including solid/hazardous waste) safeguard requirements.</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>0.8125</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>Consumption</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>Environmental-impact mitigation table, row "Hazardous waste" (impact: "Use [of] batteries, laboratory chemicals disposed haphazardly"): required mitigation measures are "Awareness raising on solid waste management with waste minimization, recovery and recycling. Ban use of plastic products in schools. Safe disposal of hazardous waste."</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>Responsible authorities explicit -- DOE/DEO/SMC are assigned overall EMP implementation and monitoring responsibility under Table 6 (+0.25 authority); monitoring explicit -- Table 11 (Operation Phase Monitoring), item 3, requires bi-annual monitoring of the "Solid waste management system" via "Records of waste collected and managed" by DEO/SMU, which directly covers this mitigation measure (+0.25 monitoring); the measure is stated without an exemption (+0.25 unconditional); no explicit fine or penalty is specified anywhere in the Framework for a school or implementing agency that fails to comply with this specific mitigation measure (0 enforcement).</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>0.875</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>Combines a Regulatory-type ban ("ban use of plastic products") with a Voluntary/persuasion element ("awareness raising ... on minimization, recovery and recycling") and a further regulatory-type safe-disposal requirement for hazardous waste generally; highest applicable score (Regulatory, 1.0) used per Coding Rule 10, with the mixed/dual nature flagged here. This is the only provision in this Framework that names "plastic" explicitly (Plastics Relevance Filter criterion (a)). No explicit enforcement mechanism (fine/penalty) is specified for non-compliance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="120" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Environmental Management Framework (EMF) for the School Sector Reform Plan (SSRP) / School Sector Program (SSP)</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adb.org/sites/default/files/project-documents/35174-082-nep-earfab.pdf</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>To integrate environmental assessment and environmental management planning into the planning, design, implementation and monitoring of school-infrastructure sub-projects under Nepal's School Sector Reform Program/School Sector Program (construction and rehabilitation of classrooms, District Education Office buildings, libraries/laboratories, toilets, water supply and seismic retrofitting), so as to identify and mitigate the adverse environmental impacts of that infrastructure work. In relation to plastics specifically, the Framework's environmental-impact mitigation table requires that solid waste (including plastic waste) generated in schools be properly segregated, minimised, reused/recycled and disposed of, and explicitly requires banning the use of plastic products in schools as a mitigation measure for hazardous-waste-related impacts.</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>"Ban use of plastic products in schools." (Table: Anticipated Environmental Impacts / Mitigation Measures, row "Hazardous waste", under Section D "Anticipated Environmental Impacts"). This is a plastics-specific commitment but is not expressed as a quantified/numeric target (e.g. a percentage reduction), so Column E is coded 0.5 rather than 1.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>This is a donor-harmonised "Environmental Management Framework" (EMF) -- explicitly stated to be "equivalent to [ADB's] Environmental Assessment and Review Framework (EARF)" under ADB's 2009 Safeguard Policy Statement (footnote 2) -- prepared originally in May 2009 and updated (per this source document, ADB project document 35174-082-NEP) for the subsequent School Sector Program, with formal approval by the Ministry of Education (Table 6, item 1.1: "Approval of EMF for SSP -- MOE"). It is a programmatic safeguard framework tied to development-partner financing conditionality, not an Act of Parliament nor a Gazette-published executive regulation, so it does not qualify for the 0.75/1.0 tiers. It is coded at the higher "plan/programme incorporating quantifiable targets" tier (0.50) rather than the purely aspirational tier (0.25) because it contains multiple quantified operational elements -- an itemised implementation budget (Table 8) and monitoring indicators with defined frequencies (Tables 9-11) -- even though its specific plastics-related commitment (the in-school plastic ban) is not itself a quantified target.</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>education, waste management, health, water, construction, disaster risk management, energy</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>consumption, recycling, disposal, environmental leakage</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Section F.4, "Budgetary Requirement" / Table 8 "Cost for Implementation of EMF": a specific, itemised budget is set out for EMF implementation -- USD 5,000 for EMF translation, printing, publication and distribution; USD 25,000 for setting up a safeguard desk in DOE and DEOs; USD 100,000 for capacity building of MOE/DOE/DEOs/SMCs; environmental screening and EMP preparation costs of approximately USD 2,000 per Initial Environmental Examination (IEE) and USD 500 per Environmental Due Diligence Report (DDR), to be included in subproject costs; and environmental monitoring costs of USD 1,000 per subproject, also included in subproject costs. Coded 1 (ring-fenced) because this is a dedicated, itemised budget line created specifically for implementing this Framework's own environmental (including solid/hazardous waste) safeguard requirements.</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>0.8125</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>Waste management</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>Environmental-impact mitigation table, row "Solid waste management" (impact: "Spreading of waste, pungent smell, deterioration of aesthetics"): required mitigation measures are "Proper solid waste management system shall be introduced in schools with segregation of waste, and its proper disposal. Encourage composting to use in school garden."</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>Responsible authorities explicit (DOE/DEO/SMC, Table 6) (+0.25 authority); monitoring explicit -- Table 11, item 3, bi-annual monitoring of the solid waste management system via records of waste collected/managed (+0.25 monitoring); the measure is mandatory ("shall be introduced") without a stated exemption (+0.25 unconditional); no explicit fine/penalty for non-compliance (0 enforcement).</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>0.875</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>A general mandatory school-level source-segregation and proper-disposal requirement that, in practice, applies to the plastic component of school solid waste streams (Plastics Relevance Filter criterion (c)); composting promotion is a complementary reuse-of-organics measure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="120" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Environmental Management Framework (EMF) for the School Sector Reform Plan (SSRP) / School Sector Program (SSP)</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adb.org/sites/default/files/project-documents/35174-082-nep-earfab.pdf</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>To integrate environmental assessment and environmental management planning into the planning, design, implementation and monitoring of school-infrastructure sub-projects under Nepal's School Sector Reform Program/School Sector Program (construction and rehabilitation of classrooms, District Education Office buildings, libraries/laboratories, toilets, water supply and seismic retrofitting), so as to identify and mitigate the adverse environmental impacts of that infrastructure work. In relation to plastics specifically, the Framework's environmental-impact mitigation table requires that solid waste (including plastic waste) generated in schools be properly segregated, minimised, reused/recycled and disposed of, and explicitly requires banning the use of plastic products in schools as a mitigation measure for hazardous-waste-related impacts.</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>"Ban use of plastic products in schools." (Table: Anticipated Environmental Impacts / Mitigation Measures, row "Hazardous waste", under Section D "Anticipated Environmental Impacts"). This is a plastics-specific commitment but is not expressed as a quantified/numeric target (e.g. a percentage reduction), so Column E is coded 0.5 rather than 1.</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>This is a donor-harmonised "Environmental Management Framework" (EMF) -- explicitly stated to be "equivalent to [ADB's] Environmental Assessment and Review Framework (EARF)" under ADB's 2009 Safeguard Policy Statement (footnote 2) -- prepared originally in May 2009 and updated (per this source document, ADB project document 35174-082-NEP) for the subsequent School Sector Program, with formal approval by the Ministry of Education (Table 6, item 1.1: "Approval of EMF for SSP -- MOE"). It is a programmatic safeguard framework tied to development-partner financing conditionality, not an Act of Parliament nor a Gazette-published executive regulation, so it does not qualify for the 0.75/1.0 tiers. It is coded at the higher "plan/programme incorporating quantifiable targets" tier (0.50) rather than the purely aspirational tier (0.25) because it contains multiple quantified operational elements -- an itemised implementation budget (Table 8) and monitoring indicators with defined frequencies (Tables 9-11) -- even though its specific plastics-related commitment (the in-school plastic ban) is not itself a quantified target.</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>education, waste management, health, water, construction, disaster risk management, energy</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>consumption, recycling, disposal, environmental leakage</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Section F.4, "Budgetary Requirement" / Table 8 "Cost for Implementation of EMF": a specific, itemised budget is set out for EMF implementation -- USD 5,000 for EMF translation, printing, publication and distribution; USD 25,000 for setting up a safeguard desk in DOE and DEOs; USD 100,000 for capacity building of MOE/DOE/DEOs/SMCs; environmental screening and EMP preparation costs of approximately USD 2,000 per Initial Environmental Examination (IEE) and USD 500 per Environmental Due Diligence Report (DDR), to be included in subproject costs; and environmental monitoring costs of USD 1,000 per subproject, also included in subproject costs. Coded 1 (ring-fenced) because this is a dedicated, itemised budget line created specifically for implementing this Framework's own environmental (including solid/hazardous waste) safeguard requirements.</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>0.8125</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>Waste management</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>Section F "Institutional Arrangement and Mechanism for Implementation of EMP" (Tables 6-7): establishes a multi-level implementation and compliance chain -- the Ministry of Education (MOE) as executing agency with overall coordination responsibility; the Department of Education (DOE) as implementing agency, which will recruit a full-time Environmental Officer and set up a "safeguard desk"; District Education Offices (DEOs), which will set up their own safeguard desks and conduct routine EMP monitoring; and School Management Committees (SMCs), which implement EMF requirements at the school level. DOE conducts quarterly EMP monitoring feeding into the government's quarterly portfolio review, and MOE/DOE conduct an annual central-level compliance audit.</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>Authority explicit and multi-tiered (MOE/DOE/DEO/SMC roles individually defined in Table 6) (+0.25 authority); monitoring explicit and extensive -- quarterly DOE-supervised DEO monitoring, annual MOE/DOE compliance audits, and annual reporting/feedback workshops (+0.25 monitoring); the institutional mechanism applies without a stated exemption (+0.25 unconditional); no explicit fine/penalty is specified for an implementing agency's own non-compliance with the coordination mechanism itself (0 enforcement; note a separate contract-breach remedy exists against contractors/SMC chairpersons for construction-quality issues, but that is not an environmental-compliance enforcement tool).</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>0.575</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>A textbook multi-level governance coordination and institutional-setup instrument under Coding Rule 11 (national ministry -&gt; department -&gt; district office -&gt; school-level committee), scored Procedural (0.40). This is the institutional backbone through which the plastic-ban and solid-waste-management instruments above are actually implemented and monitored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="120" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Environmental Management Framework (EMF) for the School Sector Reform Plan (SSRP) / School Sector Program (SSP)</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adb.org/sites/default/files/project-documents/35174-082-nep-earfab.pdf</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>To integrate environmental assessment and environmental management planning into the planning, design, implementation and monitoring of school-infrastructure sub-projects under Nepal's School Sector Reform Program/School Sector Program (construction and rehabilitation of classrooms, District Education Office buildings, libraries/laboratories, toilets, water supply and seismic retrofitting), so as to identify and mitigate the adverse environmental impacts of that infrastructure work. In relation to plastics specifically, the Framework's environmental-impact mitigation table requires that solid waste (including plastic waste) generated in schools be properly segregated, minimised, reused/recycled and disposed of, and explicitly requires banning the use of plastic products in schools as a mitigation measure for hazardous-waste-related impacts.</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>"Ban use of plastic products in schools." (Table: Anticipated Environmental Impacts / Mitigation Measures, row "Hazardous waste", under Section D "Anticipated Environmental Impacts"). This is a plastics-specific commitment but is not expressed as a quantified/numeric target (e.g. a percentage reduction), so Column E is coded 0.5 rather than 1.</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>This is a donor-harmonised "Environmental Management Framework" (EMF) -- explicitly stated to be "equivalent to [ADB's] Environmental Assessment and Review Framework (EARF)" under ADB's 2009 Safeguard Policy Statement (footnote 2) -- prepared originally in May 2009 and updated (per this source document, ADB project document 35174-082-NEP) for the subsequent School Sector Program, with formal approval by the Ministry of Education (Table 6, item 1.1: "Approval of EMF for SSP -- MOE"). It is a programmatic safeguard framework tied to development-partner financing conditionality, not an Act of Parliament nor a Gazette-published executive regulation, so it does not qualify for the 0.75/1.0 tiers. It is coded at the higher "plan/programme incorporating quantifiable targets" tier (0.50) rather than the purely aspirational tier (0.25) because it contains multiple quantified operational elements -- an itemised implementation budget (Table 8) and monitoring indicators with defined frequencies (Tables 9-11) -- even though its specific plastics-related commitment (the in-school plastic ban) is not itself a quantified target.</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>education, waste management, health, water, construction, disaster risk management, energy</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>consumption, recycling, disposal, environmental leakage</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Section F.4, "Budgetary Requirement" / Table 8 "Cost for Implementation of EMF": a specific, itemised budget is set out for EMF implementation -- USD 5,000 for EMF translation, printing, publication and distribution; USD 25,000 for setting up a safeguard desk in DOE and DEOs; USD 100,000 for capacity building of MOE/DOE/DEOs/SMCs; environmental screening and EMP preparation costs of approximately USD 2,000 per Initial Environmental Examination (IEE) and USD 500 per Environmental Due Diligence Report (DDR), to be included in subproject costs; and environmental monitoring costs of USD 1,000 per subproject, also included in subproject costs. Coded 1 (ring-fenced) because this is a dedicated, itemised budget line created specifically for implementing this Framework's own environmental (including solid/hazardous waste) safeguard requirements.</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>0.8125</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>Waste management</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>Section F.4 / Table 8 "Cost for Implementation of EMF": a specific tentative budget for EMF implementation capacity, including USD 5,000 for translation/printing/distribution, USD 25,000 for safeguard-desk setup, USD 100,000 for capacity building, and per-subproject allocations for environmental screening/assessment (~USD 2,000 per IEE, ~USD 500 per DDR) and monitoring (~USD 1,000 per subproject) -- funding that in practice supports implementation of the solid/hazardous waste (including plastic) mitigation measures identified above.</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>Authority explicit (DOE/MOE as budget-holder) (+0.25 authority); the budget is explicitly introduced as "tentative" and stated to "may include" the listed items ("The tentative budgetary requirement for implementation of EMF may include as presented in following Table 8"), i.e. framed as an indicative estimate rather than a firm, unconditional commitment (0 for unconditional); no monitoring mechanism is specified for tracking the budget's own execution/disbursement (0 monitoring); no enforcement mechanism attaches to under-spending or non-disbursement (0 enforcement).</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>Scored as Planned government/donor investment (0.80) given the specific dollar-denominated capacity/implementation investment, but coded not-in-force (S=0) because of the explicit "tentative ... may include" framing, which reads as an indicative planning estimate rather than a binding allocation (Rule 12's 'may' test). This instrument-level in-force finding does not affect the separate policy-level budget coding (Column M), which asks only whether a budget/funding source is mentioned and ring-fenced -- which it is, via this same itemised table.</t>
         </is>
       </c>
     </row>
@@ -7799,4 +8268,628 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="55" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="55" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
+    <col width="55" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="55" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="55" customWidth="1" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>A: policy_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>B: policy_url</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>C: policy_year</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>D: policy_objective</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>E: policy_target</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>F: policy_target_text</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>G: policy_type</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>H: policy_type_justification</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>I: policy_integration</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>J: policy_sectors_list</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>K: policy_circularity</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>L: policy_lifecycle_phases_list</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>M: policy_budget</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>N: policy_budget_text</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>O: policy_score</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>P: instrument_type</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Q: instrument_lifecycle_stage</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>R: instrument_description</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>S: instrument_in_force</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>T: instrument_implementation</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>U: instrument_implementation_text</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>V: instrument_score</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>W: comments</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="120" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Environmental Management Framework (EMF) for the School Sector Reform Plan (SSRP) / School Sector Program (SSP)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adb.org/sites/default/files/project-documents/35174-082-nep-earfab.pdf</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>To integrate environmental assessment and environmental management planning into the planning, design, implementation and monitoring of school-infrastructure sub-projects under Nepal's School Sector Reform Program/School Sector Program (construction and rehabilitation of classrooms, District Education Office buildings, libraries/laboratories, toilets, water supply and seismic retrofitting), so as to identify and mitigate the adverse environmental impacts of that infrastructure work. In relation to plastics specifically, the Framework's environmental-impact mitigation table requires that solid waste (including plastic waste) generated in schools be properly segregated, minimised, reused/recycled and disposed of, and explicitly requires banning the use of plastic products in schools as a mitigation measure for hazardous-waste-related impacts.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>"Ban use of plastic products in schools." (Table: Anticipated Environmental Impacts / Mitigation Measures, row "Hazardous waste", under Section D "Anticipated Environmental Impacts"). This is a plastics-specific commitment but is not expressed as a quantified/numeric target (e.g. a percentage reduction), so Column E is coded 0.5 rather than 1.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>This is a donor-harmonised "Environmental Management Framework" (EMF) -- explicitly stated to be "equivalent to [ADB's] Environmental Assessment and Review Framework (EARF)" under ADB's 2009 Safeguard Policy Statement (footnote 2) -- prepared originally in May 2009 and updated (per this source document, ADB project document 35174-082-NEP) for the subsequent School Sector Program, with formal approval by the Ministry of Education (Table 6, item 1.1: "Approval of EMF for SSP -- MOE"). It is a programmatic safeguard framework tied to development-partner financing conditionality, not an Act of Parliament nor a Gazette-published executive regulation, so it does not qualify for the 0.75/1.0 tiers. It is coded at the higher "plan/programme incorporating quantifiable targets" tier (0.50) rather than the purely aspirational tier (0.25) because it contains multiple quantified operational elements -- an itemised implementation budget (Table 8) and monitoring indicators with defined frequencies (Tables 9-11) -- even though its specific plastics-related commitment (the in-school plastic ban) is not itself a quantified target.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>education, waste management, health, water, construction, disaster risk management, energy</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>consumption, recycling, disposal, environmental leakage</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Section F.4, "Budgetary Requirement" / Table 8 "Cost for Implementation of EMF": a specific, itemised budget is set out for EMF implementation -- USD 5,000 for EMF translation, printing, publication and distribution; USD 25,000 for setting up a safeguard desk in DOE and DEOs; USD 100,000 for capacity building of MOE/DOE/DEOs/SMCs; environmental screening and EMP preparation costs of approximately USD 2,000 per Initial Environmental Examination (IEE) and USD 500 per Environmental Due Diligence Report (DDR), to be included in subproject costs; and environmental monitoring costs of USD 1,000 per subproject, also included in subproject costs. Coded 1 (ring-fenced) because this is a dedicated, itemised budget line created specifically for implementing this Framework's own environmental (including solid/hazardous waste) safeguard requirements.</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>0.8125</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Consumption</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Environmental-impact mitigation table, row "Hazardous waste" (impact: "Use [of] batteries, laboratory chemicals disposed haphazardly"): required mitigation measures are "Awareness raising on solid waste management with waste minimization, recovery and recycling. Ban use of plastic products in schools. Safe disposal of hazardous waste."</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>Responsible authorities explicit -- DOE/DEO/SMC are assigned overall EMP implementation and monitoring responsibility under Table 6 (+0.25 authority); monitoring explicit -- Table 11 (Operation Phase Monitoring), item 3, requires bi-annual monitoring of the "Solid waste management system" via "Records of waste collected and managed" by DEO/SMU, which directly covers this mitigation measure (+0.25 monitoring); the measure is stated without an exemption (+0.25 unconditional); no explicit fine or penalty is specified anywhere in the Framework for a school or implementing agency that fails to comply with this specific mitigation measure (0 enforcement).</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>0.875</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>Combines a Regulatory-type ban ("ban use of plastic products") with a Voluntary/persuasion element ("awareness raising ... on minimization, recovery and recycling") and a further regulatory-type safe-disposal requirement for hazardous waste generally; highest applicable score (Regulatory, 1.0) used per Coding Rule 10, with the mixed/dual nature flagged here. This is the only provision in this Framework that names "plastic" explicitly (Plastics Relevance Filter criterion (a)). No explicit enforcement mechanism (fine/penalty) is specified for non-compliance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="120" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Environmental Management Framework (EMF) for the School Sector Reform Plan (SSRP) / School Sector Program (SSP)</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adb.org/sites/default/files/project-documents/35174-082-nep-earfab.pdf</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>To integrate environmental assessment and environmental management planning into the planning, design, implementation and monitoring of school-infrastructure sub-projects under Nepal's School Sector Reform Program/School Sector Program (construction and rehabilitation of classrooms, District Education Office buildings, libraries/laboratories, toilets, water supply and seismic retrofitting), so as to identify and mitigate the adverse environmental impacts of that infrastructure work. In relation to plastics specifically, the Framework's environmental-impact mitigation table requires that solid waste (including plastic waste) generated in schools be properly segregated, minimised, reused/recycled and disposed of, and explicitly requires banning the use of plastic products in schools as a mitigation measure for hazardous-waste-related impacts.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>"Ban use of plastic products in schools." (Table: Anticipated Environmental Impacts / Mitigation Measures, row "Hazardous waste", under Section D "Anticipated Environmental Impacts"). This is a plastics-specific commitment but is not expressed as a quantified/numeric target (e.g. a percentage reduction), so Column E is coded 0.5 rather than 1.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>This is a donor-harmonised "Environmental Management Framework" (EMF) -- explicitly stated to be "equivalent to [ADB's] Environmental Assessment and Review Framework (EARF)" under ADB's 2009 Safeguard Policy Statement (footnote 2) -- prepared originally in May 2009 and updated (per this source document, ADB project document 35174-082-NEP) for the subsequent School Sector Program, with formal approval by the Ministry of Education (Table 6, item 1.1: "Approval of EMF for SSP -- MOE"). It is a programmatic safeguard framework tied to development-partner financing conditionality, not an Act of Parliament nor a Gazette-published executive regulation, so it does not qualify for the 0.75/1.0 tiers. It is coded at the higher "plan/programme incorporating quantifiable targets" tier (0.50) rather than the purely aspirational tier (0.25) because it contains multiple quantified operational elements -- an itemised implementation budget (Table 8) and monitoring indicators with defined frequencies (Tables 9-11) -- even though its specific plastics-related commitment (the in-school plastic ban) is not itself a quantified target.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>education, waste management, health, water, construction, disaster risk management, energy</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>consumption, recycling, disposal, environmental leakage</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Section F.4, "Budgetary Requirement" / Table 8 "Cost for Implementation of EMF": a specific, itemised budget is set out for EMF implementation -- USD 5,000 for EMF translation, printing, publication and distribution; USD 25,000 for setting up a safeguard desk in DOE and DEOs; USD 100,000 for capacity building of MOE/DOE/DEOs/SMCs; environmental screening and EMP preparation costs of approximately USD 2,000 per Initial Environmental Examination (IEE) and USD 500 per Environmental Due Diligence Report (DDR), to be included in subproject costs; and environmental monitoring costs of USD 1,000 per subproject, also included in subproject costs. Coded 1 (ring-fenced) because this is a dedicated, itemised budget line created specifically for implementing this Framework's own environmental (including solid/hazardous waste) safeguard requirements.</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>0.8125</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Waste management</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>Environmental-impact mitigation table, row "Solid waste management" (impact: "Spreading of waste, pungent smell, deterioration of aesthetics"): required mitigation measures are "Proper solid waste management system shall be introduced in schools with segregation of waste, and its proper disposal. Encourage composting to use in school garden."</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>Responsible authorities explicit (DOE/DEO/SMC, Table 6) (+0.25 authority); monitoring explicit -- Table 11, item 3, bi-annual monitoring of the solid waste management system via records of waste collected/managed (+0.25 monitoring); the measure is mandatory ("shall be introduced") without a stated exemption (+0.25 unconditional); no explicit fine/penalty for non-compliance (0 enforcement).</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>0.875</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>A general mandatory school-level source-segregation and proper-disposal requirement that, in practice, applies to the plastic component of school solid waste streams (Plastics Relevance Filter criterion (c)); composting promotion is a complementary reuse-of-organics measure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="120" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Environmental Management Framework (EMF) for the School Sector Reform Plan (SSRP) / School Sector Program (SSP)</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adb.org/sites/default/files/project-documents/35174-082-nep-earfab.pdf</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>To integrate environmental assessment and environmental management planning into the planning, design, implementation and monitoring of school-infrastructure sub-projects under Nepal's School Sector Reform Program/School Sector Program (construction and rehabilitation of classrooms, District Education Office buildings, libraries/laboratories, toilets, water supply and seismic retrofitting), so as to identify and mitigate the adverse environmental impacts of that infrastructure work. In relation to plastics specifically, the Framework's environmental-impact mitigation table requires that solid waste (including plastic waste) generated in schools be properly segregated, minimised, reused/recycled and disposed of, and explicitly requires banning the use of plastic products in schools as a mitigation measure for hazardous-waste-related impacts.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>"Ban use of plastic products in schools." (Table: Anticipated Environmental Impacts / Mitigation Measures, row "Hazardous waste", under Section D "Anticipated Environmental Impacts"). This is a plastics-specific commitment but is not expressed as a quantified/numeric target (e.g. a percentage reduction), so Column E is coded 0.5 rather than 1.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>This is a donor-harmonised "Environmental Management Framework" (EMF) -- explicitly stated to be "equivalent to [ADB's] Environmental Assessment and Review Framework (EARF)" under ADB's 2009 Safeguard Policy Statement (footnote 2) -- prepared originally in May 2009 and updated (per this source document, ADB project document 35174-082-NEP) for the subsequent School Sector Program, with formal approval by the Ministry of Education (Table 6, item 1.1: "Approval of EMF for SSP -- MOE"). It is a programmatic safeguard framework tied to development-partner financing conditionality, not an Act of Parliament nor a Gazette-published executive regulation, so it does not qualify for the 0.75/1.0 tiers. It is coded at the higher "plan/programme incorporating quantifiable targets" tier (0.50) rather than the purely aspirational tier (0.25) because it contains multiple quantified operational elements -- an itemised implementation budget (Table 8) and monitoring indicators with defined frequencies (Tables 9-11) -- even though its specific plastics-related commitment (the in-school plastic ban) is not itself a quantified target.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>education, waste management, health, water, construction, disaster risk management, energy</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>consumption, recycling, disposal, environmental leakage</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Section F.4, "Budgetary Requirement" / Table 8 "Cost for Implementation of EMF": a specific, itemised budget is set out for EMF implementation -- USD 5,000 for EMF translation, printing, publication and distribution; USD 25,000 for setting up a safeguard desk in DOE and DEOs; USD 100,000 for capacity building of MOE/DOE/DEOs/SMCs; environmental screening and EMP preparation costs of approximately USD 2,000 per Initial Environmental Examination (IEE) and USD 500 per Environmental Due Diligence Report (DDR), to be included in subproject costs; and environmental monitoring costs of USD 1,000 per subproject, also included in subproject costs. Coded 1 (ring-fenced) because this is a dedicated, itemised budget line created specifically for implementing this Framework's own environmental (including solid/hazardous waste) safeguard requirements.</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0.8125</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Waste management</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>Section F "Institutional Arrangement and Mechanism for Implementation of EMP" (Tables 6-7): establishes a multi-level implementation and compliance chain -- the Ministry of Education (MOE) as executing agency with overall coordination responsibility; the Department of Education (DOE) as implementing agency, which will recruit a full-time Environmental Officer and set up a "safeguard desk"; District Education Offices (DEOs), which will set up their own safeguard desks and conduct routine EMP monitoring; and School Management Committees (SMCs), which implement EMF requirements at the school level. DOE conducts quarterly EMP monitoring feeding into the government's quarterly portfolio review, and MOE/DOE conduct an annual central-level compliance audit.</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>Authority explicit and multi-tiered (MOE/DOE/DEO/SMC roles individually defined in Table 6) (+0.25 authority); monitoring explicit and extensive -- quarterly DOE-supervised DEO monitoring, annual MOE/DOE compliance audits, and annual reporting/feedback workshops (+0.25 monitoring); the institutional mechanism applies without a stated exemption (+0.25 unconditional); no explicit fine/penalty is specified for an implementing agency's own non-compliance with the coordination mechanism itself (0 enforcement; note a separate contract-breach remedy exists against contractors/SMC chairpersons for construction-quality issues, but that is not an environmental-compliance enforcement tool).</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>0.575</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>A textbook multi-level governance coordination and institutional-setup instrument under Coding Rule 11 (national ministry -&gt; department -&gt; district office -&gt; school-level committee), scored Procedural (0.40). This is the institutional backbone through which the plastic-ban and solid-waste-management instruments above are actually implemented and monitored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="120" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Environmental Management Framework (EMF) for the School Sector Reform Plan (SSRP) / School Sector Program (SSP)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adb.org/sites/default/files/project-documents/35174-082-nep-earfab.pdf</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>To integrate environmental assessment and environmental management planning into the planning, design, implementation and monitoring of school-infrastructure sub-projects under Nepal's School Sector Reform Program/School Sector Program (construction and rehabilitation of classrooms, District Education Office buildings, libraries/laboratories, toilets, water supply and seismic retrofitting), so as to identify and mitigate the adverse environmental impacts of that infrastructure work. In relation to plastics specifically, the Framework's environmental-impact mitigation table requires that solid waste (including plastic waste) generated in schools be properly segregated, minimised, reused/recycled and disposed of, and explicitly requires banning the use of plastic products in schools as a mitigation measure for hazardous-waste-related impacts.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>"Ban use of plastic products in schools." (Table: Anticipated Environmental Impacts / Mitigation Measures, row "Hazardous waste", under Section D "Anticipated Environmental Impacts"). This is a plastics-specific commitment but is not expressed as a quantified/numeric target (e.g. a percentage reduction), so Column E is coded 0.5 rather than 1.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>This is a donor-harmonised "Environmental Management Framework" (EMF) -- explicitly stated to be "equivalent to [ADB's] Environmental Assessment and Review Framework (EARF)" under ADB's 2009 Safeguard Policy Statement (footnote 2) -- prepared originally in May 2009 and updated (per this source document, ADB project document 35174-082-NEP) for the subsequent School Sector Program, with formal approval by the Ministry of Education (Table 6, item 1.1: "Approval of EMF for SSP -- MOE"). It is a programmatic safeguard framework tied to development-partner financing conditionality, not an Act of Parliament nor a Gazette-published executive regulation, so it does not qualify for the 0.75/1.0 tiers. It is coded at the higher "plan/programme incorporating quantifiable targets" tier (0.50) rather than the purely aspirational tier (0.25) because it contains multiple quantified operational elements -- an itemised implementation budget (Table 8) and monitoring indicators with defined frequencies (Tables 9-11) -- even though its specific plastics-related commitment (the in-school plastic ban) is not itself a quantified target.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>education, waste management, health, water, construction, disaster risk management, energy</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>consumption, recycling, disposal, environmental leakage</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Section F.4, "Budgetary Requirement" / Table 8 "Cost for Implementation of EMF": a specific, itemised budget is set out for EMF implementation -- USD 5,000 for EMF translation, printing, publication and distribution; USD 25,000 for setting up a safeguard desk in DOE and DEOs; USD 100,000 for capacity building of MOE/DOE/DEOs/SMCs; environmental screening and EMP preparation costs of approximately USD 2,000 per Initial Environmental Examination (IEE) and USD 500 per Environmental Due Diligence Report (DDR), to be included in subproject costs; and environmental monitoring costs of USD 1,000 per subproject, also included in subproject costs. Coded 1 (ring-fenced) because this is a dedicated, itemised budget line created specifically for implementing this Framework's own environmental (including solid/hazardous waste) safeguard requirements.</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0.8125</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Waste management</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>Section F.4 / Table 8 "Cost for Implementation of EMF": a specific tentative budget for EMF implementation capacity, including USD 5,000 for translation/printing/distribution, USD 25,000 for safeguard-desk setup, USD 100,000 for capacity building, and per-subproject allocations for environmental screening/assessment (~USD 2,000 per IEE, ~USD 500 per DDR) and monitoring (~USD 1,000 per subproject) -- funding that in practice supports implementation of the solid/hazardous waste (including plastic) mitigation measures identified above.</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>Authority explicit (DOE/MOE as budget-holder) (+0.25 authority); the budget is explicitly introduced as "tentative" and stated to "may include" the listed items ("The tentative budgetary requirement for implementation of EMF may include as presented in following Table 8"), i.e. framed as an indicative estimate rather than a firm, unconditional commitment (0 for unconditional); no monitoring mechanism is specified for tracking the budget's own execution/disbursement (0 monitoring); no enforcement mechanism attaches to under-spending or non-disbursement (0 enforcement).</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>Scored as Planned government/donor investment (0.80) given the specific dollar-denominated capacity/implementation investment, but coded not-in-force (S=0) because of the explicit "tentative ... may include" framing, which reads as an indicative planning estimate rather than a binding allocation (Rule 12's 'may' test). This instrument-level in-force finding does not affect the separate policy-level budget coding (Column M), which asks only whether a budget/funding source is mentioned and ring-fenced -- which it is, via this same itemised table.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/policies/4p-index/nepal-4p-index-master.xlsx
+++ b/policies/4p-index/nepal-4p-index-master.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Waste Mgmt Natl Policy 2079" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Solid Waste Mgmt Act 2068" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Sixteenth Plan 2024-29" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="EMF School Sector Program" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="EMF SSRP 2015" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W34"/>
+  <dimension ref="A1:W35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3879,22 +3879,22 @@
     <row r="31" ht="120" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Environmental Management Framework (EMF) for the School Sector Reform Plan (SSRP) / School Sector Program (SSP)</t>
+          <t>Environmental Management Framework for School Sector Reform Program (SSRP), Nepal</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>https://www.adb.org/sites/default/files/project-documents/35174-082-nep-earfab.pdf</t>
+          <t>https://www.doe.gov.np/assets/uploads/files/febc6a8f5678ba863d9ea8648d905511.pdf</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>To integrate environmental assessment and environmental management planning into the planning, design, implementation and monitoring of school-infrastructure sub-projects under Nepal's School Sector Reform Program/School Sector Program (construction and rehabilitation of classrooms, District Education Office buildings, libraries/laboratories, toilets, water supply and seismic retrofitting), so as to identify and mitigate the adverse environmental impacts of that infrastructure work. In relation to plastics specifically, the Framework's environmental-impact mitigation table requires that solid waste (including plastic waste) generated in schools be properly segregated, minimised, reused/recycled and disposed of, and explicitly requires banning the use of plastic products in schools as a mitigation measure for hazardous-waste-related impacts.</t>
+          <t>To assess and mitigate the environmental and social impacts of school physical-infrastructure construction and rehabilitation activities under Nepal's School Sector Reform Plan (SSRP) -- a World-Bank-co-financed sectoral program -- by establishing procedures for environmental screening, an Environmental Management Plan (EMP) for sub-projects, mitigation measures, and monitoring. In relation to plastics specifically, the Framework's mitigation-measures table commits to introducing proper solid-waste management (including source segregation and composting) in schools, promoting awareness that discourages the use of plastic products, promoting the use of recycled materials, and encouraging safe disposal of hazardous waste (e.g. batteries, laboratory chemicals) generated at school sites.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3904,27 +3904,27 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>"Ban use of plastic products in schools." (Table: Anticipated Environmental Impacts / Mitigation Measures, row "Hazardous waste", under Section D "Anticipated Environmental Impacts"). This is a plastics-specific commitment but is not expressed as a quantified/numeric target (e.g. a percentage reduction), so Column E is coded 0.5 rather than 1.</t>
+          <t>"Awareness regarding the management of solid waste, discouraging use of plastic products etc should be promoted in schools[.] The use of recycled materials should be promoted." (Chapter III, Table 3.2, 'Environmental and Social Mitigation Measures,' Solid waste management row).</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>This is a donor-harmonised "Environmental Management Framework" (EMF) -- explicitly stated to be "equivalent to [ADB's] Environmental Assessment and Review Framework (EARF)" under ADB's 2009 Safeguard Policy Statement (footnote 2) -- prepared originally in May 2009 and updated (per this source document, ADB project document 35174-082-NEP) for the subsequent School Sector Program, with formal approval by the Ministry of Education (Table 6, item 1.1: "Approval of EMF for SSP -- MOE"). It is a programmatic safeguard framework tied to development-partner financing conditionality, not an Act of Parliament nor a Gazette-published executive regulation, so it does not qualify for the 0.75/1.0 tiers. It is coded at the higher "plan/programme incorporating quantifiable targets" tier (0.50) rather than the purely aspirational tier (0.25) because it contains multiple quantified operational elements -- an itemised implementation budget (Table 8) and monitoring indicators with defined frequencies (Tables 9-11) -- even though its specific plastics-related commitment (the in-school plastic ban) is not itself a quantified target.</t>
+          <t>A donor-co-financed (World Bank) sectoral Environmental Management Framework/safeguard document prepared by Nepal's Department of Education (Ministry of Education), to be approved by the Ministry of Education and disclosed with the Bank (Section 3.6, 'Disclosure': "The revised EMF will be shared by the MOE with concerned stakeholders[.] After the incorporation of comments and approval from the Bank..."). It is not enacted by Parliament and is not itself an executive regulation with independent legal force -- it is a strategy/safeguard-planning document. It sets out mitigation measures and a monitoring plan (mostly using recommendatory 'should' language) without any plastics/waste-specific quantifiable target -&gt; coded at the aspirational tier (0.25) rather than the 'plan with quantifiable targets' tier (0.50), since the specific plastics/waste-relevant commitments found are qualitative rather than numeric.</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>education, waste management, health, water, construction, disaster risk management, energy</t>
+          <t>education, construction, water supply, sanitation, waste management, energy</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -3934,84 +3934,80 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>consumption, recycling, disposal, environmental leakage</t>
+          <t>consumption, recycling, disposal</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>Section F.4, "Budgetary Requirement" / Table 8 "Cost for Implementation of EMF": a specific, itemised budget is set out for EMF implementation -- USD 5,000 for EMF translation, printing, publication and distribution; USD 25,000 for setting up a safeguard desk in DOE and DEOs; USD 100,000 for capacity building of MOE/DOE/DEOs/SMCs; environmental screening and EMP preparation costs of approximately USD 2,000 per Initial Environmental Examination (IEE) and USD 500 per Environmental Due Diligence Report (DDR), to be included in subproject costs; and environmental monitoring costs of USD 1,000 per subproject, also included in subproject costs. Coded 1 (ring-fenced) because this is a dedicated, itemised budget line created specifically for implementing this Framework's own environmental (including solid/hazardous waste) safeguard requirements.</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0.8125</t>
+          <t>0.4375</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>Consumption</t>
+          <t>Waste management</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>Environmental-impact mitigation table, row "Hazardous waste" (impact: "Use [of] batteries, laboratory chemicals disposed haphazardly"): required mitigation measures are "Awareness raising on solid waste management with waste minimization, recovery and recycling. Ban use of plastic products in schools. Safe disposal of hazardous waste."</t>
+          <t>Table 3.2 (Environmental and Social Mitigation Measures), 'Solid waste management' row: "Proper solid waste management system should be introduced in schools which includes segregation of waste, and its proper disposal. The environmentally friendly management measures like composting should be encouraged. Awareness regarding the management of solid waste, discouraging use of plastic products etc should be promoted in schools[.] The use of recycled materials should be promoted."</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>Responsible authorities explicit -- DOE/DEO/SMC are assigned overall EMP implementation and monitoring responsibility under Table 6 (+0.25 authority); monitoring explicit -- Table 11 (Operation Phase Monitoring), item 3, requires bi-annual monitoring of the "Solid waste management system" via "Records of waste collected and managed" by DEO/SMU, which directly covers this mitigation measure (+0.25 monitoring); the measure is stated without an exemption (+0.25 unconditional); no explicit fine or penalty is specified anywhere in the Framework for a school or implementing agency that fails to comply with this specific mitigation measure (0 enforcement).</t>
+          <t>No specific responsible authority, enforcement mechanism, or monitoring process is named within this mitigation-measure cell itself (a related, separately-coded monitoring indicator for solid waste segregation does exist elsewhere in the document -- see Instrument 4); the measure is stated without an exemption (+0.25 unconditional).</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>Combines a Regulatory-type ban ("ban use of plastic products") with a Voluntary/persuasion element ("awareness raising ... on minimization, recovery and recycling") and a further regulatory-type safe-disposal requirement for hazardous waste generally; highest applicable score (Regulatory, 1.0) used per Coding Rule 10, with the mixed/dual nature flagged here. This is the only provision in this Framework that names "plastic" explicitly (Plastics Relevance Filter criterion (a)). No explicit enforcement mechanism (fine/penalty) is specified for non-compliance.</t>
+          <t>Uses recommendatory language throughout ('should be introduced/encouraged/promoted'), not mandatory language ('shall'/'must') -&gt; not in force per Rule 12's language test. Combines procedural elements (introducing a segregation/disposal system) with voluntary/persuasion elements (discouraging plastic use, promoting recycled materials, awareness-raising); highest applicable type (Procedural, 0.40) used per Coding Rule 10, with the dual nature flagged here.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="120" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Environmental Management Framework (EMF) for the School Sector Reform Plan (SSRP) / School Sector Program (SSP)</t>
+          <t>Environmental Management Framework for School Sector Reform Program (SSRP), Nepal</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>https://www.adb.org/sites/default/files/project-documents/35174-082-nep-earfab.pdf</t>
+          <t>https://www.doe.gov.np/assets/uploads/files/febc6a8f5678ba863d9ea8648d905511.pdf</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>To integrate environmental assessment and environmental management planning into the planning, design, implementation and monitoring of school-infrastructure sub-projects under Nepal's School Sector Reform Program/School Sector Program (construction and rehabilitation of classrooms, District Education Office buildings, libraries/laboratories, toilets, water supply and seismic retrofitting), so as to identify and mitigate the adverse environmental impacts of that infrastructure work. In relation to plastics specifically, the Framework's environmental-impact mitigation table requires that solid waste (including plastic waste) generated in schools be properly segregated, minimised, reused/recycled and disposed of, and explicitly requires banning the use of plastic products in schools as a mitigation measure for hazardous-waste-related impacts.</t>
+          <t>To assess and mitigate the environmental and social impacts of school physical-infrastructure construction and rehabilitation activities under Nepal's School Sector Reform Plan (SSRP) -- a World-Bank-co-financed sectoral program -- by establishing procedures for environmental screening, an Environmental Management Plan (EMP) for sub-projects, mitigation measures, and monitoring. In relation to plastics specifically, the Framework's mitigation-measures table commits to introducing proper solid-waste management (including source segregation and composting) in schools, promoting awareness that discourages the use of plastic products, promoting the use of recycled materials, and encouraging safe disposal of hazardous waste (e.g. batteries, laboratory chemicals) generated at school sites.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4021,27 +4017,27 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>"Ban use of plastic products in schools." (Table: Anticipated Environmental Impacts / Mitigation Measures, row "Hazardous waste", under Section D "Anticipated Environmental Impacts"). This is a plastics-specific commitment but is not expressed as a quantified/numeric target (e.g. a percentage reduction), so Column E is coded 0.5 rather than 1.</t>
+          <t>"Awareness regarding the management of solid waste, discouraging use of plastic products etc should be promoted in schools[.] The use of recycled materials should be promoted." (Chapter III, Table 3.2, 'Environmental and Social Mitigation Measures,' Solid waste management row).</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>This is a donor-harmonised "Environmental Management Framework" (EMF) -- explicitly stated to be "equivalent to [ADB's] Environmental Assessment and Review Framework (EARF)" under ADB's 2009 Safeguard Policy Statement (footnote 2) -- prepared originally in May 2009 and updated (per this source document, ADB project document 35174-082-NEP) for the subsequent School Sector Program, with formal approval by the Ministry of Education (Table 6, item 1.1: "Approval of EMF for SSP -- MOE"). It is a programmatic safeguard framework tied to development-partner financing conditionality, not an Act of Parliament nor a Gazette-published executive regulation, so it does not qualify for the 0.75/1.0 tiers. It is coded at the higher "plan/programme incorporating quantifiable targets" tier (0.50) rather than the purely aspirational tier (0.25) because it contains multiple quantified operational elements -- an itemised implementation budget (Table 8) and monitoring indicators with defined frequencies (Tables 9-11) -- even though its specific plastics-related commitment (the in-school plastic ban) is not itself a quantified target.</t>
+          <t>A donor-co-financed (World Bank) sectoral Environmental Management Framework/safeguard document prepared by Nepal's Department of Education (Ministry of Education), to be approved by the Ministry of Education and disclosed with the Bank (Section 3.6, 'Disclosure': "The revised EMF will be shared by the MOE with concerned stakeholders[.] After the incorporation of comments and approval from the Bank..."). It is not enacted by Parliament and is not itself an executive regulation with independent legal force -- it is a strategy/safeguard-planning document. It sets out mitigation measures and a monitoring plan (mostly using recommendatory 'should' language) without any plastics/waste-specific quantifiable target -&gt; coded at the aspirational tier (0.25) rather than the 'plan with quantifiable targets' tier (0.50), since the specific plastics/waste-relevant commitments found are qualitative rather than numeric.</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>education, waste management, health, water, construction, disaster risk management, energy</t>
+          <t>education, construction, water supply, sanitation, waste management, energy</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -4051,84 +4047,80 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>consumption, recycling, disposal, environmental leakage</t>
+          <t>consumption, recycling, disposal</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>Section F.4, "Budgetary Requirement" / Table 8 "Cost for Implementation of EMF": a specific, itemised budget is set out for EMF implementation -- USD 5,000 for EMF translation, printing, publication and distribution; USD 25,000 for setting up a safeguard desk in DOE and DEOs; USD 100,000 for capacity building of MOE/DOE/DEOs/SMCs; environmental screening and EMP preparation costs of approximately USD 2,000 per Initial Environmental Examination (IEE) and USD 500 per Environmental Due Diligence Report (DDR), to be included in subproject costs; and environmental monitoring costs of USD 1,000 per subproject, also included in subproject costs. Coded 1 (ring-fenced) because this is a dedicated, itemised budget line created specifically for implementing this Framework's own environmental (including solid/hazardous waste) safeguard requirements.</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0.8125</t>
+          <t>0.4375</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>Waste management</t>
+          <t>End of life</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>Environmental-impact mitigation table, row "Solid waste management" (impact: "Spreading of waste, pungent smell, deterioration of aesthetics"): required mitigation measures are "Proper solid waste management system shall be introduced in schools with segregation of waste, and its proper disposal. Encourage composting to use in school garden."</t>
+          <t>Table 3.2, 'Hazardous waste' row: "Use [of] batteries, laboratory chemicals etc[.] Safe disposal of hazardous waste should be encouraged." Cross-referenced by Annex 10 (Laboratory Checklist from Environmental Perspective), which screens whether a laboratory has "proper waste disposal facilities," "adequate liquid waste management facilities," and "proper storage facilities for hazardous chemicals, pesticides etc."</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>Responsible authorities explicit (DOE/DEO/SMC, Table 6) (+0.25 authority); monitoring explicit -- Table 11, item 3, bi-annual monitoring of the solid waste management system via records of waste collected/managed (+0.25 monitoring); the measure is mandatory ("shall be introduced") without a stated exemption (+0.25 unconditional); no explicit fine/penalty for non-compliance (0 enforcement).</t>
+          <t>No specific authority, enforcement, or monitoring mechanism is named for this specific mitigation measure; stated without an exemption (+0.25 unconditional).</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>A general mandatory school-level source-segregation and proper-disposal requirement that, in practice, applies to the plastic component of school solid waste streams (Plastics Relevance Filter criterion (c)); composting promotion is a complementary reuse-of-organics measure.</t>
+          <t>Purely persuasive/voluntary language ('should be encouraged') -&gt; Voluntary measures/persuasion (0.20); not in force.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="120" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Environmental Management Framework (EMF) for the School Sector Reform Plan (SSRP) / School Sector Program (SSP)</t>
+          <t>Environmental Management Framework for School Sector Reform Program (SSRP), Nepal</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>https://www.adb.org/sites/default/files/project-documents/35174-082-nep-earfab.pdf</t>
+          <t>https://www.doe.gov.np/assets/uploads/files/febc6a8f5678ba863d9ea8648d905511.pdf</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>To integrate environmental assessment and environmental management planning into the planning, design, implementation and monitoring of school-infrastructure sub-projects under Nepal's School Sector Reform Program/School Sector Program (construction and rehabilitation of classrooms, District Education Office buildings, libraries/laboratories, toilets, water supply and seismic retrofitting), so as to identify and mitigate the adverse environmental impacts of that infrastructure work. In relation to plastics specifically, the Framework's environmental-impact mitigation table requires that solid waste (including plastic waste) generated in schools be properly segregated, minimised, reused/recycled and disposed of, and explicitly requires banning the use of plastic products in schools as a mitigation measure for hazardous-waste-related impacts.</t>
+          <t>To assess and mitigate the environmental and social impacts of school physical-infrastructure construction and rehabilitation activities under Nepal's School Sector Reform Plan (SSRP) -- a World-Bank-co-financed sectoral program -- by establishing procedures for environmental screening, an Environmental Management Plan (EMP) for sub-projects, mitigation measures, and monitoring. In relation to plastics specifically, the Framework's mitigation-measures table commits to introducing proper solid-waste management (including source segregation and composting) in schools, promoting awareness that discourages the use of plastic products, promoting the use of recycled materials, and encouraging safe disposal of hazardous waste (e.g. batteries, laboratory chemicals) generated at school sites.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -4138,114 +4130,110 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>"Ban use of plastic products in schools." (Table: Anticipated Environmental Impacts / Mitigation Measures, row "Hazardous waste", under Section D "Anticipated Environmental Impacts"). This is a plastics-specific commitment but is not expressed as a quantified/numeric target (e.g. a percentage reduction), so Column E is coded 0.5 rather than 1.</t>
+          <t>"Awareness regarding the management of solid waste, discouraging use of plastic products etc should be promoted in schools[.] The use of recycled materials should be promoted." (Chapter III, Table 3.2, 'Environmental and Social Mitigation Measures,' Solid waste management row).</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>A donor-co-financed (World Bank) sectoral Environmental Management Framework/safeguard document prepared by Nepal's Department of Education (Ministry of Education), to be approved by the Ministry of Education and disclosed with the Bank (Section 3.6, 'Disclosure': "The revised EMF will be shared by the MOE with concerned stakeholders[.] After the incorporation of comments and approval from the Bank..."). It is not enacted by Parliament and is not itself an executive regulation with independent legal force -- it is a strategy/safeguard-planning document. It sets out mitigation measures and a monitoring plan (mostly using recommendatory 'should' language) without any plastics/waste-specific quantifiable target -&gt; coded at the aspirational tier (0.25) rather than the 'plan with quantifiable targets' tier (0.50), since the specific plastics/waste-relevant commitments found are qualitative rather than numeric.</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>education, construction, water supply, sanitation, waste management, energy</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>consumption, recycling, disposal</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>0.4375</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>Waste management</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>Section 2.7 ('Mechanisms for Implementation of EMF in SSRP') and Section 3.5 ('Integration of EMF into regular programs'): environmental screening of sub-project activities (by DEO), incorporation of Environmental Management Plan (EMP) requirements into School Improvement Plan (SIP) preparation guidelines and tender/contract documents, and mandatory EMP preparation for any SSRP sub-component built through tendering ("The EMP must be prepared if SSRP sub component has to be constructed through tendering"). Supported by Annex 10's laboratory environmental screening checklist, which specifically screens for hazardous/liquid/infectious waste generation.</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
           <t>0.50</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>This is a donor-harmonised "Environmental Management Framework" (EMF) -- explicitly stated to be "equivalent to [ADB's] Environmental Assessment and Review Framework (EARF)" under ADB's 2009 Safeguard Policy Statement (footnote 2) -- prepared originally in May 2009 and updated (per this source document, ADB project document 35174-082-NEP) for the subsequent School Sector Program, with formal approval by the Ministry of Education (Table 6, item 1.1: "Approval of EMF for SSP -- MOE"). It is a programmatic safeguard framework tied to development-partner financing conditionality, not an Act of Parliament nor a Gazette-published executive regulation, so it does not qualify for the 0.75/1.0 tiers. It is coded at the higher "plan/programme incorporating quantifiable targets" tier (0.50) rather than the purely aspirational tier (0.25) because it contains multiple quantified operational elements -- an itemised implementation budget (Table 8) and monitoring indicators with defined frequencies (Tables 9-11) -- even though its specific plastics-related commitment (the in-school plastic ban) is not itself a quantified target.</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>education, waste management, health, water, construction, disaster risk management, energy</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>consumption, recycling, disposal, environmental leakage</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>Section F.4, "Budgetary Requirement" / Table 8 "Cost for Implementation of EMF": a specific, itemised budget is set out for EMF implementation -- USD 5,000 for EMF translation, printing, publication and distribution; USD 25,000 for setting up a safeguard desk in DOE and DEOs; USD 100,000 for capacity building of MOE/DOE/DEOs/SMCs; environmental screening and EMP preparation costs of approximately USD 2,000 per Initial Environmental Examination (IEE) and USD 500 per Environmental Due Diligence Report (DDR), to be included in subproject costs; and environmental monitoring costs of USD 1,000 per subproject, also included in subproject costs. Coded 1 (ring-fenced) because this is a dedicated, itemised budget line created specifically for implementing this Framework's own environmental (including solid/hazardous waste) safeguard requirements.</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>0.8125</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>Waste management</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>Section F "Institutional Arrangement and Mechanism for Implementation of EMP" (Tables 6-7): establishes a multi-level implementation and compliance chain -- the Ministry of Education (MOE) as executing agency with overall coordination responsibility; the Department of Education (DOE) as implementing agency, which will recruit a full-time Environmental Officer and set up a "safeguard desk"; District Education Offices (DEOs), which will set up their own safeguard desks and conduct routine EMP monitoring; and School Management Committees (SMCs), which implement EMF requirements at the school level. DOE conducts quarterly EMP monitoring feeding into the government's quarterly portfolio review, and MOE/DOE conduct an annual central-level compliance audit.</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>Authority explicit and multi-tiered (MOE/DOE/DEO/SMC roles individually defined in Table 6) (+0.25 authority); monitoring explicit and extensive -- quarterly DOE-supervised DEO monitoring, annual MOE/DOE compliance audits, and annual reporting/feedback workshops (+0.25 monitoring); the institutional mechanism applies without a stated exemption (+0.25 unconditional); no explicit fine/penalty is specified for an implementing agency's own non-compliance with the coordination mechanism itself (0 enforcement; note a separate contract-breach remedy exists against contractors/SMC chairpersons for construction-quality issues, but that is not an environmental-compliance enforcement tool).</t>
+          <t>Authority explicit (DEO conducts screening; DOE incorporates EMF into SIP guidelines; MoE approves the EMF) (+0.25); no explicit fine/penalty is specified for skipping the EMP process (0); monitoring is explicit via the separate Field-Level Monitoring, Sub-Project-Level Monitoring and annual Compliance Audit mechanisms described in the same section (+0.25); NOT scored unconditional because Section 2.7 explicitly exempts small-threshold construction from EMP/EA requirements ("No special EA is required as construction activities are of very small threshold, i.e. less than NRs 825,000.00") (0).</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>A textbook multi-level governance coordination and institutional-setup instrument under Coding Rule 11 (national ministry -&gt; department -&gt; district office -&gt; school-level committee), scored Procedural (0.40). This is the institutional backbone through which the plastic-ban and solid-waste-management instruments above are actually implemented and monitored.</t>
+          <t>A procedural/planning-requirement instrument (screening + EMP) -- matches the Procedural (0.40) tier's own 'planning requirements' example. Scored in force because Section 3.5 uses mandatory language ('must be prepared') for the EMP requirement, notwithstanding the small-project exemption noted above.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="120" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Environmental Management Framework (EMF) for the School Sector Reform Plan (SSRP) / School Sector Program (SSP)</t>
+          <t>Environmental Management Framework for School Sector Reform Program (SSRP), Nepal</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>https://www.adb.org/sites/default/files/project-documents/35174-082-nep-earfab.pdf</t>
+          <t>https://www.doe.gov.np/assets/uploads/files/febc6a8f5678ba863d9ea8648d905511.pdf</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>To integrate environmental assessment and environmental management planning into the planning, design, implementation and monitoring of school-infrastructure sub-projects under Nepal's School Sector Reform Program/School Sector Program (construction and rehabilitation of classrooms, District Education Office buildings, libraries/laboratories, toilets, water supply and seismic retrofitting), so as to identify and mitigate the adverse environmental impacts of that infrastructure work. In relation to plastics specifically, the Framework's environmental-impact mitigation table requires that solid waste (including plastic waste) generated in schools be properly segregated, minimised, reused/recycled and disposed of, and explicitly requires banning the use of plastic products in schools as a mitigation measure for hazardous-waste-related impacts.</t>
+          <t>To assess and mitigate the environmental and social impacts of school physical-infrastructure construction and rehabilitation activities under Nepal's School Sector Reform Plan (SSRP) -- a World-Bank-co-financed sectoral program -- by establishing procedures for environmental screening, an Environmental Management Plan (EMP) for sub-projects, mitigation measures, and monitoring. In relation to plastics specifically, the Framework's mitigation-measures table commits to introducing proper solid-waste management (including source segregation and composting) in schools, promoting awareness that discourages the use of plastic products, promoting the use of recycled materials, and encouraging safe disposal of hazardous waste (e.g. batteries, laboratory chemicals) generated at school sites.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4255,27 +4243,27 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>"Ban use of plastic products in schools." (Table: Anticipated Environmental Impacts / Mitigation Measures, row "Hazardous waste", under Section D "Anticipated Environmental Impacts"). This is a plastics-specific commitment but is not expressed as a quantified/numeric target (e.g. a percentage reduction), so Column E is coded 0.5 rather than 1.</t>
+          <t>"Awareness regarding the management of solid waste, discouraging use of plastic products etc should be promoted in schools[.] The use of recycled materials should be promoted." (Chapter III, Table 3.2, 'Environmental and Social Mitigation Measures,' Solid waste management row).</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>This is a donor-harmonised "Environmental Management Framework" (EMF) -- explicitly stated to be "equivalent to [ADB's] Environmental Assessment and Review Framework (EARF)" under ADB's 2009 Safeguard Policy Statement (footnote 2) -- prepared originally in May 2009 and updated (per this source document, ADB project document 35174-082-NEP) for the subsequent School Sector Program, with formal approval by the Ministry of Education (Table 6, item 1.1: "Approval of EMF for SSP -- MOE"). It is a programmatic safeguard framework tied to development-partner financing conditionality, not an Act of Parliament nor a Gazette-published executive regulation, so it does not qualify for the 0.75/1.0 tiers. It is coded at the higher "plan/programme incorporating quantifiable targets" tier (0.50) rather than the purely aspirational tier (0.25) because it contains multiple quantified operational elements -- an itemised implementation budget (Table 8) and monitoring indicators with defined frequencies (Tables 9-11) -- even though its specific plastics-related commitment (the in-school plastic ban) is not itself a quantified target.</t>
+          <t>A donor-co-financed (World Bank) sectoral Environmental Management Framework/safeguard document prepared by Nepal's Department of Education (Ministry of Education), to be approved by the Ministry of Education and disclosed with the Bank (Section 3.6, 'Disclosure': "The revised EMF will be shared by the MOE with concerned stakeholders[.] After the incorporation of comments and approval from the Bank..."). It is not enacted by Parliament and is not itself an executive regulation with independent legal force -- it is a strategy/safeguard-planning document. It sets out mitigation measures and a monitoring plan (mostly using recommendatory 'should' language) without any plastics/waste-specific quantifiable target -&gt; coded at the aspirational tier (0.25) rather than the 'plan with quantifiable targets' tier (0.50), since the specific plastics/waste-relevant commitments found are qualitative rather than numeric.</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>education, waste management, health, water, construction, disaster risk management, energy</t>
+          <t>education, construction, water supply, sanitation, waste management, energy</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -4285,27 +4273,23 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>consumption, recycling, disposal, environmental leakage</t>
+          <t>consumption, recycling, disposal</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>Section F.4, "Budgetary Requirement" / Table 8 "Cost for Implementation of EMF": a specific, itemised budget is set out for EMF implementation -- USD 5,000 for EMF translation, printing, publication and distribution; USD 25,000 for setting up a safeguard desk in DOE and DEOs; USD 100,000 for capacity building of MOE/DOE/DEOs/SMCs; environmental screening and EMP preparation costs of approximately USD 2,000 per Initial Environmental Examination (IEE) and USD 500 per Environmental Due Diligence Report (DDR), to be included in subproject costs; and environmental monitoring costs of USD 1,000 per subproject, also included in subproject costs. Coded 1 (ring-fenced) because this is a dedicated, itemised budget line created specifically for implementing this Framework's own environmental (including solid/hazardous waste) safeguard requirements.</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0.8125</t>
+          <t>0.4375</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4315,32 +4299,145 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>Section F.4 / Table 8 "Cost for Implementation of EMF": a specific tentative budget for EMF implementation capacity, including USD 5,000 for translation/printing/distribution, USD 25,000 for safeguard-desk setup, USD 100,000 for capacity building, and per-subproject allocations for environmental screening/assessment (~USD 2,000 per IEE, ~USD 500 per DDR) and monitoring (~USD 1,000 per subproject) -- funding that in practice supports implementation of the solid/hazardous waste (including plastic) mitigation measures identified above.</t>
+          <t>Section 3.4 ('Monitoring Plan'), Construction Phase Monitoring table, item 6: 'Solid waste segregation disposal' -- Type/Method of Monitoring: 'CM/Direct Observation'; Frequency: 'Everyday'; Monitoring Responsibility: 'SMC' (School Management Committee).</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>Authority explicit (SMC, as monitoring responsibility) (+0.25); no explicit fine/penalty attaches to a failure to conduct this specific daily monitoring (0); a second-tier compliance-audit mechanism exists over the whole monitoring system (Section 2.7, item 3(c): "Compliance Audit... Annually... Verifies overall compliance to EMF") (+0.25 monitoring-of-monitoring); the monitoring frequency ('Everyday') is stated without an exemption (+0.25 unconditional).</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>0.575</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>The single most concrete, plastics/waste-relevant, recurring implementation mechanism found in this document -- an explicit, named, daily monitoring indicator specifically for solid-waste segregation and disposal during school construction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="120" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Environmental Management Framework for School Sector Reform Program (SSRP), Nepal</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.doe.gov.np/assets/uploads/files/febc6a8f5678ba863d9ea8648d905511.pdf</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>To assess and mitigate the environmental and social impacts of school physical-infrastructure construction and rehabilitation activities under Nepal's School Sector Reform Plan (SSRP) -- a World-Bank-co-financed sectoral program -- by establishing procedures for environmental screening, an Environmental Management Plan (EMP) for sub-projects, mitigation measures, and monitoring. In relation to plastics specifically, the Framework's mitigation-measures table commits to introducing proper solid-waste management (including source segregation and composting) in schools, promoting awareness that discourages the use of plastic products, promoting the use of recycled materials, and encouraging safe disposal of hazardous waste (e.g. batteries, laboratory chemicals) generated at school sites.</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>"Awareness regarding the management of solid waste, discouraging use of plastic products etc should be promoted in schools[.] The use of recycled materials should be promoted." (Chapter III, Table 3.2, 'Environmental and Social Mitigation Measures,' Solid waste management row).</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>Authority explicit (DOE/MOE as budget-holder) (+0.25 authority); the budget is explicitly introduced as "tentative" and stated to "may include" the listed items ("The tentative budgetary requirement for implementation of EMF may include as presented in following Table 8"), i.e. framed as an indicative estimate rather than a firm, unconditional commitment (0 for unconditional); no monitoring mechanism is specified for tracking the budget's own execution/disbursement (0 monitoring); no enforcement mechanism attaches to under-spending or non-disbursement (0 enforcement).</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="inlineStr">
-        <is>
-          <t>Scored as Planned government/donor investment (0.80) given the specific dollar-denominated capacity/implementation investment, but coded not-in-force (S=0) because of the explicit "tentative ... may include" framing, which reads as an indicative planning estimate rather than a binding allocation (Rule 12's 'may' test). This instrument-level in-force finding does not affect the separate policy-level budget coding (Column M), which asks only whether a budget/funding source is mentioned and ring-fenced -- which it is, via this same itemised table.</t>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>A donor-co-financed (World Bank) sectoral Environmental Management Framework/safeguard document prepared by Nepal's Department of Education (Ministry of Education), to be approved by the Ministry of Education and disclosed with the Bank (Section 3.6, 'Disclosure': "The revised EMF will be shared by the MOE with concerned stakeholders[.] After the incorporation of comments and approval from the Bank..."). It is not enacted by Parliament and is not itself an executive regulation with independent legal force -- it is a strategy/safeguard-planning document. It sets out mitigation measures and a monitoring plan (mostly using recommendatory 'should' language) without any plastics/waste-specific quantifiable target -&gt; coded at the aspirational tier (0.25) rather than the 'plan with quantifiable targets' tier (0.50), since the specific plastics/waste-relevant commitments found are qualitative rather than numeric.</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>education, construction, water supply, sanitation, waste management, energy</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>consumption, recycling, disposal</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>0.4375</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>Waste management</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>Section 2.7 ('Mechanisms for Implementation'), Pre-Construction Monitoring item 2, and Section 2.8 ('Existing Capacity Assessment'): the Framework calls for a 'Full-time Environmental Officer in place at DoE' (tracked as a monitoring indicator, method 'Evidence,' frequency 'Once,' responsibility 'MoE/DoE') to provide environmental oversight and coordinate implementation of the EMF across schools and District Education Offices.</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>Authority/position explicitly named (Environmental Officer at DoE) (+0.25); no enforcement mechanism is specified (0); the position's establishment is itself tracked as a monitoring indicator (+0.25); stated without an exemption (+0.25 unconditional).</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>Institutional-setup instrument matching the Procedural (0.40) tier's own worked example ('a new plastic management board or any other institution'). Coded not-in-force because Section 2.8's own capacity assessment shows this position is not yet actually filled on a dedicated basis at any tier (marked 'X' -- lack of capacity -- for Manpower and Budget at MOE, DOE, DEO and SMC; a civil engineer currently absorbs environmental duties 'over and above engineering tasks'). This is therefore better characterised as an aspirational target/indicator to be achieved during implementation rather than an already-operative institutional arrangement -- flagged as a judgement call, since the document's own monitoring table treats it as something to be verified ('Evidence,' 'Once'), implying the Framework expects it to be established.</t>
         </is>
       </c>
     </row>
@@ -8276,7 +8373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -8424,22 +8521,22 @@
     <row r="2" ht="120" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Environmental Management Framework (EMF) for the School Sector Reform Plan (SSRP) / School Sector Program (SSP)</t>
+          <t>Environmental Management Framework for School Sector Reform Program (SSRP), Nepal</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://www.adb.org/sites/default/files/project-documents/35174-082-nep-earfab.pdf</t>
+          <t>https://www.doe.gov.np/assets/uploads/files/febc6a8f5678ba863d9ea8648d905511.pdf</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>To integrate environmental assessment and environmental management planning into the planning, design, implementation and monitoring of school-infrastructure sub-projects under Nepal's School Sector Reform Program/School Sector Program (construction and rehabilitation of classrooms, District Education Office buildings, libraries/laboratories, toilets, water supply and seismic retrofitting), so as to identify and mitigate the adverse environmental impacts of that infrastructure work. In relation to plastics specifically, the Framework's environmental-impact mitigation table requires that solid waste (including plastic waste) generated in schools be properly segregated, minimised, reused/recycled and disposed of, and explicitly requires banning the use of plastic products in schools as a mitigation measure for hazardous-waste-related impacts.</t>
+          <t>To assess and mitigate the environmental and social impacts of school physical-infrastructure construction and rehabilitation activities under Nepal's School Sector Reform Plan (SSRP) -- a World-Bank-co-financed sectoral program -- by establishing procedures for environmental screening, an Environmental Management Plan (EMP) for sub-projects, mitigation measures, and monitoring. In relation to plastics specifically, the Framework's mitigation-measures table commits to introducing proper solid-waste management (including source segregation and composting) in schools, promoting awareness that discourages the use of plastic products, promoting the use of recycled materials, and encouraging safe disposal of hazardous waste (e.g. batteries, laboratory chemicals) generated at school sites.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -8449,27 +8546,27 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>"Ban use of plastic products in schools." (Table: Anticipated Environmental Impacts / Mitigation Measures, row "Hazardous waste", under Section D "Anticipated Environmental Impacts"). This is a plastics-specific commitment but is not expressed as a quantified/numeric target (e.g. a percentage reduction), so Column E is coded 0.5 rather than 1.</t>
+          <t>"Awareness regarding the management of solid waste, discouraging use of plastic products etc should be promoted in schools[.] The use of recycled materials should be promoted." (Chapter III, Table 3.2, 'Environmental and Social Mitigation Measures,' Solid waste management row).</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>This is a donor-harmonised "Environmental Management Framework" (EMF) -- explicitly stated to be "equivalent to [ADB's] Environmental Assessment and Review Framework (EARF)" under ADB's 2009 Safeguard Policy Statement (footnote 2) -- prepared originally in May 2009 and updated (per this source document, ADB project document 35174-082-NEP) for the subsequent School Sector Program, with formal approval by the Ministry of Education (Table 6, item 1.1: "Approval of EMF for SSP -- MOE"). It is a programmatic safeguard framework tied to development-partner financing conditionality, not an Act of Parliament nor a Gazette-published executive regulation, so it does not qualify for the 0.75/1.0 tiers. It is coded at the higher "plan/programme incorporating quantifiable targets" tier (0.50) rather than the purely aspirational tier (0.25) because it contains multiple quantified operational elements -- an itemised implementation budget (Table 8) and monitoring indicators with defined frequencies (Tables 9-11) -- even though its specific plastics-related commitment (the in-school plastic ban) is not itself a quantified target.</t>
+          <t>A donor-co-financed (World Bank) sectoral Environmental Management Framework/safeguard document prepared by Nepal's Department of Education (Ministry of Education), to be approved by the Ministry of Education and disclosed with the Bank (Section 3.6, 'Disclosure': "The revised EMF will be shared by the MOE with concerned stakeholders[.] After the incorporation of comments and approval from the Bank..."). It is not enacted by Parliament and is not itself an executive regulation with independent legal force -- it is a strategy/safeguard-planning document. It sets out mitigation measures and a monitoring plan (mostly using recommendatory 'should' language) without any plastics/waste-specific quantifiable target -&gt; coded at the aspirational tier (0.25) rather than the 'plan with quantifiable targets' tier (0.50), since the specific plastics/waste-relevant commitments found are qualitative rather than numeric.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>education, waste management, health, water, construction, disaster risk management, energy</t>
+          <t>education, construction, water supply, sanitation, waste management, energy</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -8479,84 +8576,80 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>consumption, recycling, disposal, environmental leakage</t>
+          <t>consumption, recycling, disposal</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Section F.4, "Budgetary Requirement" / Table 8 "Cost for Implementation of EMF": a specific, itemised budget is set out for EMF implementation -- USD 5,000 for EMF translation, printing, publication and distribution; USD 25,000 for setting up a safeguard desk in DOE and DEOs; USD 100,000 for capacity building of MOE/DOE/DEOs/SMCs; environmental screening and EMP preparation costs of approximately USD 2,000 per Initial Environmental Examination (IEE) and USD 500 per Environmental Due Diligence Report (DDR), to be included in subproject costs; and environmental monitoring costs of USD 1,000 per subproject, also included in subproject costs. Coded 1 (ring-fenced) because this is a dedicated, itemised budget line created specifically for implementing this Framework's own environmental (including solid/hazardous waste) safeguard requirements.</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>0.8125</t>
+          <t>0.4375</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Consumption</t>
+          <t>Waste management</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>Environmental-impact mitigation table, row "Hazardous waste" (impact: "Use [of] batteries, laboratory chemicals disposed haphazardly"): required mitigation measures are "Awareness raising on solid waste management with waste minimization, recovery and recycling. Ban use of plastic products in schools. Safe disposal of hazardous waste."</t>
+          <t>Table 3.2 (Environmental and Social Mitigation Measures), 'Solid waste management' row: "Proper solid waste management system should be introduced in schools which includes segregation of waste, and its proper disposal. The environmentally friendly management measures like composting should be encouraged. Awareness regarding the management of solid waste, discouraging use of plastic products etc should be promoted in schools[.] The use of recycled materials should be promoted."</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>Responsible authorities explicit -- DOE/DEO/SMC are assigned overall EMP implementation and monitoring responsibility under Table 6 (+0.25 authority); monitoring explicit -- Table 11 (Operation Phase Monitoring), item 3, requires bi-annual monitoring of the "Solid waste management system" via "Records of waste collected and managed" by DEO/SMU, which directly covers this mitigation measure (+0.25 monitoring); the measure is stated without an exemption (+0.25 unconditional); no explicit fine or penalty is specified anywhere in the Framework for a school or implementing agency that fails to comply with this specific mitigation measure (0 enforcement).</t>
+          <t>No specific responsible authority, enforcement mechanism, or monitoring process is named within this mitigation-measure cell itself (a related, separately-coded monitoring indicator for solid waste segregation does exist elsewhere in the document -- see Instrument 4); the measure is stated without an exemption (+0.25 unconditional).</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>Combines a Regulatory-type ban ("ban use of plastic products") with a Voluntary/persuasion element ("awareness raising ... on minimization, recovery and recycling") and a further regulatory-type safe-disposal requirement for hazardous waste generally; highest applicable score (Regulatory, 1.0) used per Coding Rule 10, with the mixed/dual nature flagged here. This is the only provision in this Framework that names "plastic" explicitly (Plastics Relevance Filter criterion (a)). No explicit enforcement mechanism (fine/penalty) is specified for non-compliance.</t>
+          <t>Uses recommendatory language throughout ('should be introduced/encouraged/promoted'), not mandatory language ('shall'/'must') -&gt; not in force per Rule 12's language test. Combines procedural elements (introducing a segregation/disposal system) with voluntary/persuasion elements (discouraging plastic use, promoting recycled materials, awareness-raising); highest applicable type (Procedural, 0.40) used per Coding Rule 10, with the dual nature flagged here.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="120" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Environmental Management Framework (EMF) for the School Sector Reform Plan (SSRP) / School Sector Program (SSP)</t>
+          <t>Environmental Management Framework for School Sector Reform Program (SSRP), Nepal</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>https://www.adb.org/sites/default/files/project-documents/35174-082-nep-earfab.pdf</t>
+          <t>https://www.doe.gov.np/assets/uploads/files/febc6a8f5678ba863d9ea8648d905511.pdf</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>To integrate environmental assessment and environmental management planning into the planning, design, implementation and monitoring of school-infrastructure sub-projects under Nepal's School Sector Reform Program/School Sector Program (construction and rehabilitation of classrooms, District Education Office buildings, libraries/laboratories, toilets, water supply and seismic retrofitting), so as to identify and mitigate the adverse environmental impacts of that infrastructure work. In relation to plastics specifically, the Framework's environmental-impact mitigation table requires that solid waste (including plastic waste) generated in schools be properly segregated, minimised, reused/recycled and disposed of, and explicitly requires banning the use of plastic products in schools as a mitigation measure for hazardous-waste-related impacts.</t>
+          <t>To assess and mitigate the environmental and social impacts of school physical-infrastructure construction and rehabilitation activities under Nepal's School Sector Reform Plan (SSRP) -- a World-Bank-co-financed sectoral program -- by establishing procedures for environmental screening, an Environmental Management Plan (EMP) for sub-projects, mitigation measures, and monitoring. In relation to plastics specifically, the Framework's mitigation-measures table commits to introducing proper solid-waste management (including source segregation and composting) in schools, promoting awareness that discourages the use of plastic products, promoting the use of recycled materials, and encouraging safe disposal of hazardous waste (e.g. batteries, laboratory chemicals) generated at school sites.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -8566,27 +8659,27 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>"Ban use of plastic products in schools." (Table: Anticipated Environmental Impacts / Mitigation Measures, row "Hazardous waste", under Section D "Anticipated Environmental Impacts"). This is a plastics-specific commitment but is not expressed as a quantified/numeric target (e.g. a percentage reduction), so Column E is coded 0.5 rather than 1.</t>
+          <t>"Awareness regarding the management of solid waste, discouraging use of plastic products etc should be promoted in schools[.] The use of recycled materials should be promoted." (Chapter III, Table 3.2, 'Environmental and Social Mitigation Measures,' Solid waste management row).</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>This is a donor-harmonised "Environmental Management Framework" (EMF) -- explicitly stated to be "equivalent to [ADB's] Environmental Assessment and Review Framework (EARF)" under ADB's 2009 Safeguard Policy Statement (footnote 2) -- prepared originally in May 2009 and updated (per this source document, ADB project document 35174-082-NEP) for the subsequent School Sector Program, with formal approval by the Ministry of Education (Table 6, item 1.1: "Approval of EMF for SSP -- MOE"). It is a programmatic safeguard framework tied to development-partner financing conditionality, not an Act of Parliament nor a Gazette-published executive regulation, so it does not qualify for the 0.75/1.0 tiers. It is coded at the higher "plan/programme incorporating quantifiable targets" tier (0.50) rather than the purely aspirational tier (0.25) because it contains multiple quantified operational elements -- an itemised implementation budget (Table 8) and monitoring indicators with defined frequencies (Tables 9-11) -- even though its specific plastics-related commitment (the in-school plastic ban) is not itself a quantified target.</t>
+          <t>A donor-co-financed (World Bank) sectoral Environmental Management Framework/safeguard document prepared by Nepal's Department of Education (Ministry of Education), to be approved by the Ministry of Education and disclosed with the Bank (Section 3.6, 'Disclosure': "The revised EMF will be shared by the MOE with concerned stakeholders[.] After the incorporation of comments and approval from the Bank..."). It is not enacted by Parliament and is not itself an executive regulation with independent legal force -- it is a strategy/safeguard-planning document. It sets out mitigation measures and a monitoring plan (mostly using recommendatory 'should' language) without any plastics/waste-specific quantifiable target -&gt; coded at the aspirational tier (0.25) rather than the 'plan with quantifiable targets' tier (0.50), since the specific plastics/waste-relevant commitments found are qualitative rather than numeric.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>education, waste management, health, water, construction, disaster risk management, energy</t>
+          <t>education, construction, water supply, sanitation, waste management, energy</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -8596,84 +8689,80 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>consumption, recycling, disposal, environmental leakage</t>
+          <t>consumption, recycling, disposal</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Section F.4, "Budgetary Requirement" / Table 8 "Cost for Implementation of EMF": a specific, itemised budget is set out for EMF implementation -- USD 5,000 for EMF translation, printing, publication and distribution; USD 25,000 for setting up a safeguard desk in DOE and DEOs; USD 100,000 for capacity building of MOE/DOE/DEOs/SMCs; environmental screening and EMP preparation costs of approximately USD 2,000 per Initial Environmental Examination (IEE) and USD 500 per Environmental Due Diligence Report (DDR), to be included in subproject costs; and environmental monitoring costs of USD 1,000 per subproject, also included in subproject costs. Coded 1 (ring-fenced) because this is a dedicated, itemised budget line created specifically for implementing this Framework's own environmental (including solid/hazardous waste) safeguard requirements.</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>0.8125</t>
+          <t>0.4375</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Waste management</t>
+          <t>End of life</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>Environmental-impact mitigation table, row "Solid waste management" (impact: "Spreading of waste, pungent smell, deterioration of aesthetics"): required mitigation measures are "Proper solid waste management system shall be introduced in schools with segregation of waste, and its proper disposal. Encourage composting to use in school garden."</t>
+          <t>Table 3.2, 'Hazardous waste' row: "Use [of] batteries, laboratory chemicals etc[.] Safe disposal of hazardous waste should be encouraged." Cross-referenced by Annex 10 (Laboratory Checklist from Environmental Perspective), which screens whether a laboratory has "proper waste disposal facilities," "adequate liquid waste management facilities," and "proper storage facilities for hazardous chemicals, pesticides etc."</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>Responsible authorities explicit (DOE/DEO/SMC, Table 6) (+0.25 authority); monitoring explicit -- Table 11, item 3, bi-annual monitoring of the solid waste management system via records of waste collected/managed (+0.25 monitoring); the measure is mandatory ("shall be introduced") without a stated exemption (+0.25 unconditional); no explicit fine/penalty for non-compliance (0 enforcement).</t>
+          <t>No specific authority, enforcement, or monitoring mechanism is named for this specific mitigation measure; stated without an exemption (+0.25 unconditional).</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>A general mandatory school-level source-segregation and proper-disposal requirement that, in practice, applies to the plastic component of school solid waste streams (Plastics Relevance Filter criterion (c)); composting promotion is a complementary reuse-of-organics measure.</t>
+          <t>Purely persuasive/voluntary language ('should be encouraged') -&gt; Voluntary measures/persuasion (0.20); not in force.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="120" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Environmental Management Framework (EMF) for the School Sector Reform Plan (SSRP) / School Sector Program (SSP)</t>
+          <t>Environmental Management Framework for School Sector Reform Program (SSRP), Nepal</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://www.adb.org/sites/default/files/project-documents/35174-082-nep-earfab.pdf</t>
+          <t>https://www.doe.gov.np/assets/uploads/files/febc6a8f5678ba863d9ea8648d905511.pdf</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>To integrate environmental assessment and environmental management planning into the planning, design, implementation and monitoring of school-infrastructure sub-projects under Nepal's School Sector Reform Program/School Sector Program (construction and rehabilitation of classrooms, District Education Office buildings, libraries/laboratories, toilets, water supply and seismic retrofitting), so as to identify and mitigate the adverse environmental impacts of that infrastructure work. In relation to plastics specifically, the Framework's environmental-impact mitigation table requires that solid waste (including plastic waste) generated in schools be properly segregated, minimised, reused/recycled and disposed of, and explicitly requires banning the use of plastic products in schools as a mitigation measure for hazardous-waste-related impacts.</t>
+          <t>To assess and mitigate the environmental and social impacts of school physical-infrastructure construction and rehabilitation activities under Nepal's School Sector Reform Plan (SSRP) -- a World-Bank-co-financed sectoral program -- by establishing procedures for environmental screening, an Environmental Management Plan (EMP) for sub-projects, mitigation measures, and monitoring. In relation to plastics specifically, the Framework's mitigation-measures table commits to introducing proper solid-waste management (including source segregation and composting) in schools, promoting awareness that discourages the use of plastic products, promoting the use of recycled materials, and encouraging safe disposal of hazardous waste (e.g. batteries, laboratory chemicals) generated at school sites.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -8683,114 +8772,110 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>"Ban use of plastic products in schools." (Table: Anticipated Environmental Impacts / Mitigation Measures, row "Hazardous waste", under Section D "Anticipated Environmental Impacts"). This is a plastics-specific commitment but is not expressed as a quantified/numeric target (e.g. a percentage reduction), so Column E is coded 0.5 rather than 1.</t>
+          <t>"Awareness regarding the management of solid waste, discouraging use of plastic products etc should be promoted in schools[.] The use of recycled materials should be promoted." (Chapter III, Table 3.2, 'Environmental and Social Mitigation Measures,' Solid waste management row).</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>A donor-co-financed (World Bank) sectoral Environmental Management Framework/safeguard document prepared by Nepal's Department of Education (Ministry of Education), to be approved by the Ministry of Education and disclosed with the Bank (Section 3.6, 'Disclosure': "The revised EMF will be shared by the MOE with concerned stakeholders[.] After the incorporation of comments and approval from the Bank..."). It is not enacted by Parliament and is not itself an executive regulation with independent legal force -- it is a strategy/safeguard-planning document. It sets out mitigation measures and a monitoring plan (mostly using recommendatory 'should' language) without any plastics/waste-specific quantifiable target -&gt; coded at the aspirational tier (0.25) rather than the 'plan with quantifiable targets' tier (0.50), since the specific plastics/waste-relevant commitments found are qualitative rather than numeric.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>education, construction, water supply, sanitation, waste management, energy</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>consumption, recycling, disposal</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0.4375</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Waste management</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>Section 2.7 ('Mechanisms for Implementation of EMF in SSRP') and Section 3.5 ('Integration of EMF into regular programs'): environmental screening of sub-project activities (by DEO), incorporation of Environmental Management Plan (EMP) requirements into School Improvement Plan (SIP) preparation guidelines and tender/contract documents, and mandatory EMP preparation for any SSRP sub-component built through tendering ("The EMP must be prepared if SSRP sub component has to be constructed through tendering"). Supported by Annex 10's laboratory environmental screening checklist, which specifically screens for hazardous/liquid/infectious waste generation.</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
           <t>0.50</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>This is a donor-harmonised "Environmental Management Framework" (EMF) -- explicitly stated to be "equivalent to [ADB's] Environmental Assessment and Review Framework (EARF)" under ADB's 2009 Safeguard Policy Statement (footnote 2) -- prepared originally in May 2009 and updated (per this source document, ADB project document 35174-082-NEP) for the subsequent School Sector Program, with formal approval by the Ministry of Education (Table 6, item 1.1: "Approval of EMF for SSP -- MOE"). It is a programmatic safeguard framework tied to development-partner financing conditionality, not an Act of Parliament nor a Gazette-published executive regulation, so it does not qualify for the 0.75/1.0 tiers. It is coded at the higher "plan/programme incorporating quantifiable targets" tier (0.50) rather than the purely aspirational tier (0.25) because it contains multiple quantified operational elements -- an itemised implementation budget (Table 8) and monitoring indicators with defined frequencies (Tables 9-11) -- even though its specific plastics-related commitment (the in-school plastic ban) is not itself a quantified target.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>education, waste management, health, water, construction, disaster risk management, energy</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>consumption, recycling, disposal, environmental leakage</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Section F.4, "Budgetary Requirement" / Table 8 "Cost for Implementation of EMF": a specific, itemised budget is set out for EMF implementation -- USD 5,000 for EMF translation, printing, publication and distribution; USD 25,000 for setting up a safeguard desk in DOE and DEOs; USD 100,000 for capacity building of MOE/DOE/DEOs/SMCs; environmental screening and EMP preparation costs of approximately USD 2,000 per Initial Environmental Examination (IEE) and USD 500 per Environmental Due Diligence Report (DDR), to be included in subproject costs; and environmental monitoring costs of USD 1,000 per subproject, also included in subproject costs. Coded 1 (ring-fenced) because this is a dedicated, itemised budget line created specifically for implementing this Framework's own environmental (including solid/hazardous waste) safeguard requirements.</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0.8125</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>Waste management</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>Section F "Institutional Arrangement and Mechanism for Implementation of EMP" (Tables 6-7): establishes a multi-level implementation and compliance chain -- the Ministry of Education (MOE) as executing agency with overall coordination responsibility; the Department of Education (DOE) as implementing agency, which will recruit a full-time Environmental Officer and set up a "safeguard desk"; District Education Offices (DEOs), which will set up their own safeguard desks and conduct routine EMP monitoring; and School Management Committees (SMCs), which implement EMF requirements at the school level. DOE conducts quarterly EMP monitoring feeding into the government's quarterly portfolio review, and MOE/DOE conduct an annual central-level compliance audit.</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>Authority explicit and multi-tiered (MOE/DOE/DEO/SMC roles individually defined in Table 6) (+0.25 authority); monitoring explicit and extensive -- quarterly DOE-supervised DEO monitoring, annual MOE/DOE compliance audits, and annual reporting/feedback workshops (+0.25 monitoring); the institutional mechanism applies without a stated exemption (+0.25 unconditional); no explicit fine/penalty is specified for an implementing agency's own non-compliance with the coordination mechanism itself (0 enforcement; note a separate contract-breach remedy exists against contractors/SMC chairpersons for construction-quality issues, but that is not an environmental-compliance enforcement tool).</t>
+          <t>Authority explicit (DEO conducts screening; DOE incorporates EMF into SIP guidelines; MoE approves the EMF) (+0.25); no explicit fine/penalty is specified for skipping the EMP process (0); monitoring is explicit via the separate Field-Level Monitoring, Sub-Project-Level Monitoring and annual Compliance Audit mechanisms described in the same section (+0.25); NOT scored unconditional because Section 2.7 explicitly exempts small-threshold construction from EMP/EA requirements ("No special EA is required as construction activities are of very small threshold, i.e. less than NRs 825,000.00") (0).</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>A textbook multi-level governance coordination and institutional-setup instrument under Coding Rule 11 (national ministry -&gt; department -&gt; district office -&gt; school-level committee), scored Procedural (0.40). This is the institutional backbone through which the plastic-ban and solid-waste-management instruments above are actually implemented and monitored.</t>
+          <t>A procedural/planning-requirement instrument (screening + EMP) -- matches the Procedural (0.40) tier's own 'planning requirements' example. Scored in force because Section 3.5 uses mandatory language ('must be prepared') for the EMP requirement, notwithstanding the small-project exemption noted above.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="120" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Environmental Management Framework (EMF) for the School Sector Reform Plan (SSRP) / School Sector Program (SSP)</t>
+          <t>Environmental Management Framework for School Sector Reform Program (SSRP), Nepal</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>https://www.adb.org/sites/default/files/project-documents/35174-082-nep-earfab.pdf</t>
+          <t>https://www.doe.gov.np/assets/uploads/files/febc6a8f5678ba863d9ea8648d905511.pdf</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>To integrate environmental assessment and environmental management planning into the planning, design, implementation and monitoring of school-infrastructure sub-projects under Nepal's School Sector Reform Program/School Sector Program (construction and rehabilitation of classrooms, District Education Office buildings, libraries/laboratories, toilets, water supply and seismic retrofitting), so as to identify and mitigate the adverse environmental impacts of that infrastructure work. In relation to plastics specifically, the Framework's environmental-impact mitigation table requires that solid waste (including plastic waste) generated in schools be properly segregated, minimised, reused/recycled and disposed of, and explicitly requires banning the use of plastic products in schools as a mitigation measure for hazardous-waste-related impacts.</t>
+          <t>To assess and mitigate the environmental and social impacts of school physical-infrastructure construction and rehabilitation activities under Nepal's School Sector Reform Plan (SSRP) -- a World-Bank-co-financed sectoral program -- by establishing procedures for environmental screening, an Environmental Management Plan (EMP) for sub-projects, mitigation measures, and monitoring. In relation to plastics specifically, the Framework's mitigation-measures table commits to introducing proper solid-waste management (including source segregation and composting) in schools, promoting awareness that discourages the use of plastic products, promoting the use of recycled materials, and encouraging safe disposal of hazardous waste (e.g. batteries, laboratory chemicals) generated at school sites.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -8800,27 +8885,27 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>"Ban use of plastic products in schools." (Table: Anticipated Environmental Impacts / Mitigation Measures, row "Hazardous waste", under Section D "Anticipated Environmental Impacts"). This is a plastics-specific commitment but is not expressed as a quantified/numeric target (e.g. a percentage reduction), so Column E is coded 0.5 rather than 1.</t>
+          <t>"Awareness regarding the management of solid waste, discouraging use of plastic products etc should be promoted in schools[.] The use of recycled materials should be promoted." (Chapter III, Table 3.2, 'Environmental and Social Mitigation Measures,' Solid waste management row).</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>This is a donor-harmonised "Environmental Management Framework" (EMF) -- explicitly stated to be "equivalent to [ADB's] Environmental Assessment and Review Framework (EARF)" under ADB's 2009 Safeguard Policy Statement (footnote 2) -- prepared originally in May 2009 and updated (per this source document, ADB project document 35174-082-NEP) for the subsequent School Sector Program, with formal approval by the Ministry of Education (Table 6, item 1.1: "Approval of EMF for SSP -- MOE"). It is a programmatic safeguard framework tied to development-partner financing conditionality, not an Act of Parliament nor a Gazette-published executive regulation, so it does not qualify for the 0.75/1.0 tiers. It is coded at the higher "plan/programme incorporating quantifiable targets" tier (0.50) rather than the purely aspirational tier (0.25) because it contains multiple quantified operational elements -- an itemised implementation budget (Table 8) and monitoring indicators with defined frequencies (Tables 9-11) -- even though its specific plastics-related commitment (the in-school plastic ban) is not itself a quantified target.</t>
+          <t>A donor-co-financed (World Bank) sectoral Environmental Management Framework/safeguard document prepared by Nepal's Department of Education (Ministry of Education), to be approved by the Ministry of Education and disclosed with the Bank (Section 3.6, 'Disclosure': "The revised EMF will be shared by the MOE with concerned stakeholders[.] After the incorporation of comments and approval from the Bank..."). It is not enacted by Parliament and is not itself an executive regulation with independent legal force -- it is a strategy/safeguard-planning document. It sets out mitigation measures and a monitoring plan (mostly using recommendatory 'should' language) without any plastics/waste-specific quantifiable target -&gt; coded at the aspirational tier (0.25) rather than the 'plan with quantifiable targets' tier (0.50), since the specific plastics/waste-relevant commitments found are qualitative rather than numeric.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>education, waste management, health, water, construction, disaster risk management, energy</t>
+          <t>education, construction, water supply, sanitation, waste management, energy</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -8830,27 +8915,23 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>consumption, recycling, disposal, environmental leakage</t>
+          <t>consumption, recycling, disposal</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>Section F.4, "Budgetary Requirement" / Table 8 "Cost for Implementation of EMF": a specific, itemised budget is set out for EMF implementation -- USD 5,000 for EMF translation, printing, publication and distribution; USD 25,000 for setting up a safeguard desk in DOE and DEOs; USD 100,000 for capacity building of MOE/DOE/DEOs/SMCs; environmental screening and EMP preparation costs of approximately USD 2,000 per Initial Environmental Examination (IEE) and USD 500 per Environmental Due Diligence Report (DDR), to be included in subproject costs; and environmental monitoring costs of USD 1,000 per subproject, also included in subproject costs. Coded 1 (ring-fenced) because this is a dedicated, itemised budget line created specifically for implementing this Framework's own environmental (including solid/hazardous waste) safeguard requirements.</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0.8125</t>
+          <t>0.4375</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8860,32 +8941,145 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>Section F.4 / Table 8 "Cost for Implementation of EMF": a specific tentative budget for EMF implementation capacity, including USD 5,000 for translation/printing/distribution, USD 25,000 for safeguard-desk setup, USD 100,000 for capacity building, and per-subproject allocations for environmental screening/assessment (~USD 2,000 per IEE, ~USD 500 per DDR) and monitoring (~USD 1,000 per subproject) -- funding that in practice supports implementation of the solid/hazardous waste (including plastic) mitigation measures identified above.</t>
+          <t>Section 3.4 ('Monitoring Plan'), Construction Phase Monitoring table, item 6: 'Solid waste segregation disposal' -- Type/Method of Monitoring: 'CM/Direct Observation'; Frequency: 'Everyday'; Monitoring Responsibility: 'SMC' (School Management Committee).</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>Authority explicit (SMC, as monitoring responsibility) (+0.25); no explicit fine/penalty attaches to a failure to conduct this specific daily monitoring (0); a second-tier compliance-audit mechanism exists over the whole monitoring system (Section 2.7, item 3(c): "Compliance Audit... Annually... Verifies overall compliance to EMF") (+0.25 monitoring-of-monitoring); the monitoring frequency ('Everyday') is stated without an exemption (+0.25 unconditional).</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>0.575</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>The single most concrete, plastics/waste-relevant, recurring implementation mechanism found in this document -- an explicit, named, daily monitoring indicator specifically for solid-waste segregation and disposal during school construction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="120" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Environmental Management Framework for School Sector Reform Program (SSRP), Nepal</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.doe.gov.np/assets/uploads/files/febc6a8f5678ba863d9ea8648d905511.pdf</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>To assess and mitigate the environmental and social impacts of school physical-infrastructure construction and rehabilitation activities under Nepal's School Sector Reform Plan (SSRP) -- a World-Bank-co-financed sectoral program -- by establishing procedures for environmental screening, an Environmental Management Plan (EMP) for sub-projects, mitigation measures, and monitoring. In relation to plastics specifically, the Framework's mitigation-measures table commits to introducing proper solid-waste management (including source segregation and composting) in schools, promoting awareness that discourages the use of plastic products, promoting the use of recycled materials, and encouraging safe disposal of hazardous waste (e.g. batteries, laboratory chemicals) generated at school sites.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>"Awareness regarding the management of solid waste, discouraging use of plastic products etc should be promoted in schools[.] The use of recycled materials should be promoted." (Chapter III, Table 3.2, 'Environmental and Social Mitigation Measures,' Solid waste management row).</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>Authority explicit (DOE/MOE as budget-holder) (+0.25 authority); the budget is explicitly introduced as "tentative" and stated to "may include" the listed items ("The tentative budgetary requirement for implementation of EMF may include as presented in following Table 8"), i.e. framed as an indicative estimate rather than a firm, unconditional commitment (0 for unconditional); no monitoring mechanism is specified for tracking the budget's own execution/disbursement (0 monitoring); no enforcement mechanism attaches to under-spending or non-disbursement (0 enforcement).</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>Scored as Planned government/donor investment (0.80) given the specific dollar-denominated capacity/implementation investment, but coded not-in-force (S=0) because of the explicit "tentative ... may include" framing, which reads as an indicative planning estimate rather than a binding allocation (Rule 12's 'may' test). This instrument-level in-force finding does not affect the separate policy-level budget coding (Column M), which asks only whether a budget/funding source is mentioned and ring-fenced -- which it is, via this same itemised table.</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>A donor-co-financed (World Bank) sectoral Environmental Management Framework/safeguard document prepared by Nepal's Department of Education (Ministry of Education), to be approved by the Ministry of Education and disclosed with the Bank (Section 3.6, 'Disclosure': "The revised EMF will be shared by the MOE with concerned stakeholders[.] After the incorporation of comments and approval from the Bank..."). It is not enacted by Parliament and is not itself an executive regulation with independent legal force -- it is a strategy/safeguard-planning document. It sets out mitigation measures and a monitoring plan (mostly using recommendatory 'should' language) without any plastics/waste-specific quantifiable target -&gt; coded at the aspirational tier (0.25) rather than the 'plan with quantifiable targets' tier (0.50), since the specific plastics/waste-relevant commitments found are qualitative rather than numeric.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>education, construction, water supply, sanitation, waste management, energy</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>consumption, recycling, disposal</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0.4375</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Waste management</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>Section 2.7 ('Mechanisms for Implementation'), Pre-Construction Monitoring item 2, and Section 2.8 ('Existing Capacity Assessment'): the Framework calls for a 'Full-time Environmental Officer in place at DoE' (tracked as a monitoring indicator, method 'Evidence,' frequency 'Once,' responsibility 'MoE/DoE') to provide environmental oversight and coordinate implementation of the EMF across schools and District Education Offices.</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>Authority/position explicitly named (Environmental Officer at DoE) (+0.25); no enforcement mechanism is specified (0); the position's establishment is itself tracked as a monitoring indicator (+0.25); stated without an exemption (+0.25 unconditional).</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>Institutional-setup instrument matching the Procedural (0.40) tier's own worked example ('a new plastic management board or any other institution'). Coded not-in-force because Section 2.8's own capacity assessment shows this position is not yet actually filled on a dedicated basis at any tier (marked 'X' -- lack of capacity -- for Manpower and Budget at MOE, DOE, DEO and SMC; a civil engineer currently absorbs environmental duties 'over and above engineering tasks'). This is therefore better characterised as an aspirational target/indicator to be achieved during implementation rather than an already-operative institutional arrangement -- flagged as a judgement call, since the document's own monitoring table treats it as something to be verified ('Evidence,' 'Once'), implying the Framework expects it to be established.</t>
         </is>
       </c>
     </row>
